--- a/data/trans_orig/IP06-Provincia-trans_orig.xlsx
+++ b/data/trans_orig/IP06-Provincia-trans_orig.xlsx
@@ -732,12 +732,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>2430</t>
+          <t>2390</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>9195</t>
+          <t>9371</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -747,12 +747,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>4,68%</t>
+          <t>4,61%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>17,72%</t>
+          <t>18,06%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -767,12 +767,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>3780</t>
+          <t>3983</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>12953</t>
+          <t>12310</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -782,12 +782,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>6,28%</t>
+          <t>6,62%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>21,51%</t>
+          <t>20,44%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -802,12 +802,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>7868</t>
+          <t>7990</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>18650</t>
+          <t>18914</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -817,12 +817,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>7,02%</t>
+          <t>7,13%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>16,64%</t>
+          <t>16,87%</t>
         </is>
       </c>
     </row>
@@ -958,12 +958,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>16036</t>
+          <t>15736</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>26197</t>
+          <t>26927</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -973,12 +973,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>30,91%</t>
+          <t>30,33%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>50,49%</t>
+          <t>51,9%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -993,12 +993,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>18906</t>
+          <t>18657</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>31625</t>
+          <t>31515</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1008,12 +1008,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>31,4%</t>
+          <t>30,98%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>52,52%</t>
+          <t>52,34%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1028,12 +1028,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>38323</t>
+          <t>37940</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>55887</t>
+          <t>55438</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1043,12 +1043,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>34,19%</t>
+          <t>33,84%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>49,85%</t>
+          <t>49,45%</t>
         </is>
       </c>
     </row>
@@ -1071,12 +1071,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>20450</t>
+          <t>20263</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>30657</t>
+          <t>31735</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1086,12 +1086,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>39,41%</t>
+          <t>39,05%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>59,09%</t>
+          <t>61,16%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1106,12 +1106,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>20441</t>
+          <t>21151</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>33822</t>
+          <t>33922</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1121,12 +1121,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>33,95%</t>
+          <t>35,12%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>56,17%</t>
+          <t>56,33%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1141,12 +1141,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>44412</t>
+          <t>45043</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>61376</t>
+          <t>61729</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1156,12 +1156,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>39,62%</t>
+          <t>40,18%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>54,75%</t>
+          <t>55,07%</t>
         </is>
       </c>
     </row>
@@ -1301,12 +1301,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>6113</t>
+          <t>6148</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>16591</t>
+          <t>15987</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -1316,12 +1316,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>6,1%</t>
+          <t>6,13%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>16,54%</t>
+          <t>15,94%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -1336,12 +1336,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>8955</t>
+          <t>9420</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>20192</t>
+          <t>20797</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1351,12 +1351,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>8,23%</t>
+          <t>8,66%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>18,57%</t>
+          <t>19,12%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -1371,12 +1371,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>17738</t>
+          <t>17734</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>33623</t>
+          <t>32918</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -1386,12 +1386,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>8,49%</t>
+          <t>8,48%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>16,08%</t>
+          <t>15,75%</t>
         </is>
       </c>
     </row>
@@ -1419,7 +1419,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>4657</t>
+          <t>3671</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1434,7 +1434,7 @@
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>4,64%</t>
+          <t>3,66%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1454,7 +1454,7 @@
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>4619</t>
+          <t>4482</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1469,7 +1469,7 @@
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>4,25%</t>
+          <t>4,12%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1489,7 +1489,7 @@
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>5016</t>
+          <t>5385</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1504,7 +1504,7 @@
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>2,4%</t>
+          <t>2,58%</t>
         </is>
       </c>
     </row>
@@ -1527,12 +1527,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>20451</t>
+          <t>20224</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>34462</t>
+          <t>33875</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1542,12 +1542,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>20,39%</t>
+          <t>20,17%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>34,36%</t>
+          <t>33,78%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1562,12 +1562,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>17450</t>
+          <t>17505</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>31989</t>
+          <t>31705</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1577,12 +1577,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>16,05%</t>
+          <t>16,1%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>29,41%</t>
+          <t>29,15%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1597,12 +1597,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>42070</t>
+          <t>41223</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>61149</t>
+          <t>60169</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1612,12 +1612,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>20,12%</t>
+          <t>19,72%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>29,25%</t>
+          <t>28,78%</t>
         </is>
       </c>
     </row>
@@ -1640,12 +1640,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>53778</t>
+          <t>55098</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>70020</t>
+          <t>70079</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1655,12 +1655,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>53,62%</t>
+          <t>54,94%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>69,82%</t>
+          <t>69,88%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1675,12 +1675,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>60612</t>
+          <t>60501</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>77353</t>
+          <t>76940</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1690,12 +1690,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>55,73%</t>
+          <t>55,63%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>71,12%</t>
+          <t>70,74%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1710,12 +1710,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>120087</t>
+          <t>120676</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>141325</t>
+          <t>142101</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1725,12 +1725,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>57,45%</t>
+          <t>57,73%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>67,6%</t>
+          <t>67,98%</t>
         </is>
       </c>
     </row>
@@ -1870,12 +1870,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>1368</t>
+          <t>1434</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>7704</t>
+          <t>7837</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1885,12 +1885,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>2,02%</t>
+          <t>2,12%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>11,4%</t>
+          <t>11,59%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1910,7 +1910,7 @@
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>3778</t>
+          <t>4271</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1925,7 +1925,7 @@
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>5,37%</t>
+          <t>6,07%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1940,12 +1940,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>2081</t>
+          <t>2032</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>9700</t>
+          <t>9209</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1955,12 +1955,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>1,51%</t>
+          <t>1,47%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>7,03%</t>
+          <t>6,68%</t>
         </is>
       </c>
     </row>
@@ -1988,7 +1988,7 @@
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>5501</t>
+          <t>5260</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -2003,7 +2003,7 @@
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>8,14%</t>
+          <t>7,78%</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
@@ -2023,7 +2023,7 @@
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>4034</t>
+          <t>4062</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -2038,7 +2038,7 @@
       </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t>5,74%</t>
+          <t>5,78%</t>
         </is>
       </c>
       <c r="Q15" s="2" t="inlineStr">
@@ -2053,12 +2053,12 @@
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>641</t>
+          <t>788</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>6458</t>
+          <t>7025</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -2068,12 +2068,12 @@
       </c>
       <c r="V15" s="2" t="inlineStr">
         <is>
-          <t>0,46%</t>
+          <t>0,57%</t>
         </is>
       </c>
       <c r="W15" s="2" t="inlineStr">
         <is>
-          <t>4,68%</t>
+          <t>5,09%</t>
         </is>
       </c>
     </row>
@@ -2096,12 +2096,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>14201</t>
+          <t>14327</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>26522</t>
+          <t>26309</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2111,12 +2111,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>21,01%</t>
+          <t>21,2%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>39,24%</t>
+          <t>38,92%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2131,12 +2131,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>9930</t>
+          <t>10610</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>20559</t>
+          <t>21142</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2146,12 +2146,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>14,12%</t>
+          <t>15,09%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>29,23%</t>
+          <t>30,06%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2166,12 +2166,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>26983</t>
+          <t>26567</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>44077</t>
+          <t>43161</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2181,12 +2181,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>19,56%</t>
+          <t>19,26%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>31,96%</t>
+          <t>31,29%</t>
         </is>
       </c>
     </row>
@@ -2209,12 +2209,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>35495</t>
+          <t>35425</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>48294</t>
+          <t>48960</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2224,12 +2224,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>52,51%</t>
+          <t>52,41%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>71,44%</t>
+          <t>72,43%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2244,12 +2244,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>47263</t>
+          <t>46750</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>57922</t>
+          <t>57942</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2259,12 +2259,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>67,2%</t>
+          <t>66,47%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>82,36%</t>
+          <t>82,39%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2279,12 +2279,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>85911</t>
+          <t>86511</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>104622</t>
+          <t>104586</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2294,12 +2294,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>62,29%</t>
+          <t>62,72%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>75,85%</t>
+          <t>75,83%</t>
         </is>
       </c>
     </row>
@@ -2439,12 +2439,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>1237</t>
+          <t>1071</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>6495</t>
+          <t>6849</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2454,12 +2454,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>1,65%</t>
+          <t>1,43%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>8,68%</t>
+          <t>9,15%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2474,12 +2474,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>1656</t>
+          <t>1510</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>8520</t>
+          <t>8902</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2489,12 +2489,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>2,09%</t>
+          <t>1,91%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>10,77%</t>
+          <t>11,25%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2509,12 +2509,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>4134</t>
+          <t>3891</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>12848</t>
+          <t>12809</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2524,12 +2524,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>2,68%</t>
+          <t>2,53%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>8,34%</t>
+          <t>8,32%</t>
         </is>
       </c>
     </row>
@@ -2587,12 +2587,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>670</t>
+          <t>677</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>6802</t>
+          <t>6736</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2602,12 +2602,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>0,85%</t>
+          <t>0,86%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>8,6%</t>
+          <t>8,51%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2622,12 +2622,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>685</t>
+          <t>673</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>6401</t>
+          <t>6544</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2642,7 +2642,7 @@
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>4,16%</t>
+          <t>4,25%</t>
         </is>
       </c>
     </row>
@@ -2665,12 +2665,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>21874</t>
+          <t>21219</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>35708</t>
+          <t>34342</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -2680,12 +2680,12 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>29,22%</t>
+          <t>28,34%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>47,7%</t>
+          <t>45,87%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -2700,12 +2700,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>21563</t>
+          <t>22105</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>35186</t>
+          <t>35718</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -2715,12 +2715,12 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>27,26%</t>
+          <t>27,94%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>44,48%</t>
+          <t>45,15%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -2735,12 +2735,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>47598</t>
+          <t>46806</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>66645</t>
+          <t>66638</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -2750,7 +2750,7 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>30,91%</t>
+          <t>30,4%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
@@ -2783,7 +2783,7 @@
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>50042</t>
+          <t>50282</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2798,7 +2798,7 @@
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>66,85%</t>
+          <t>67,17%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2813,12 +2813,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>36399</t>
+          <t>36705</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>51020</t>
+          <t>50888</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2828,12 +2828,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>46,01%</t>
+          <t>46,4%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>64,49%</t>
+          <t>64,32%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2848,12 +2848,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>77446</t>
+          <t>76787</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>97024</t>
+          <t>97247</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2863,12 +2863,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>50,3%</t>
+          <t>49,87%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>63,01%</t>
+          <t>63,16%</t>
         </is>
       </c>
     </row>
@@ -3008,12 +3008,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>4682</t>
+          <t>4726</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>12886</t>
+          <t>13442</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -3023,12 +3023,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>11,19%</t>
+          <t>11,29%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>30,79%</t>
+          <t>32,12%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -3043,12 +3043,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>2051</t>
+          <t>1439</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>9052</t>
+          <t>7908</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -3058,12 +3058,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>4,64%</t>
+          <t>3,26%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>20,49%</t>
+          <t>17,9%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -3078,12 +3078,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>8116</t>
+          <t>7791</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>19170</t>
+          <t>18757</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -3093,12 +3093,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>9,43%</t>
+          <t>9,06%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>22,28%</t>
+          <t>21,8%</t>
         </is>
       </c>
     </row>
@@ -3126,7 +3126,7 @@
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>3155</t>
+          <t>3684</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3141,7 +3141,7 @@
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>7,54%</t>
+          <t>8,8%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3161,7 +3161,7 @@
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>3613</t>
+          <t>3604</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -3176,7 +3176,7 @@
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>8,18%</t>
+          <t>8,16%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3196,7 +3196,7 @@
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>4602</t>
+          <t>4358</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3211,7 +3211,7 @@
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>5,35%</t>
+          <t>5,07%</t>
         </is>
       </c>
     </row>
@@ -3234,12 +3234,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>8097</t>
+          <t>8122</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>17601</t>
+          <t>17911</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3249,12 +3249,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>19,35%</t>
+          <t>19,41%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>42,06%</t>
+          <t>42,8%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3269,12 +3269,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>8890</t>
+          <t>8969</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>19310</t>
+          <t>19381</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -3284,12 +3284,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>20,12%</t>
+          <t>20,3%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>43,71%</t>
+          <t>43,87%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3304,12 +3304,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>20326</t>
+          <t>19687</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>33974</t>
+          <t>33384</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -3319,12 +3319,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>23,63%</t>
+          <t>22,88%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>39,49%</t>
+          <t>38,81%</t>
         </is>
       </c>
     </row>
@@ -3347,12 +3347,12 @@
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>15317</t>
+          <t>14839</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>25457</t>
+          <t>25507</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
@@ -3362,12 +3362,12 @@
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>36,6%</t>
+          <t>35,46%</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>60,83%</t>
+          <t>60,95%</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
@@ -3382,12 +3382,12 @@
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>20331</t>
+          <t>19819</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>30881</t>
+          <t>30366</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
@@ -3397,12 +3397,12 @@
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>46,02%</t>
+          <t>44,86%</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
         <is>
-          <t>69,9%</t>
+          <t>68,74%</t>
         </is>
       </c>
       <c r="Q27" s="2" t="inlineStr">
@@ -3417,12 +3417,12 @@
       </c>
       <c r="S27" s="2" t="inlineStr">
         <is>
-          <t>38203</t>
+          <t>38073</t>
         </is>
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>52789</t>
+          <t>52846</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
@@ -3432,12 +3432,12 @@
       </c>
       <c r="V27" s="2" t="inlineStr">
         <is>
-          <t>44,41%</t>
+          <t>44,26%</t>
         </is>
       </c>
       <c r="W27" s="2" t="inlineStr">
         <is>
-          <t>61,36%</t>
+          <t>61,43%</t>
         </is>
       </c>
     </row>
@@ -3577,12 +3577,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>5266</t>
+          <t>5253</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>13951</t>
+          <t>14138</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -3592,12 +3592,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>9,39%</t>
+          <t>9,37%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>24,89%</t>
+          <t>25,22%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -3612,12 +3612,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>1309</t>
+          <t>1292</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>7542</t>
+          <t>7493</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -3627,12 +3627,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>2,19%</t>
+          <t>2,16%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>12,63%</t>
+          <t>12,54%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -3647,12 +3647,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>7933</t>
+          <t>7847</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>18754</t>
+          <t>18671</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -3662,12 +3662,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>6,85%</t>
+          <t>6,78%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>16,2%</t>
+          <t>16,13%</t>
         </is>
       </c>
     </row>
@@ -3730,7 +3730,7 @@
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>2628</t>
+          <t>3101</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -3745,7 +3745,7 @@
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>4,4%</t>
+          <t>5,19%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -3765,7 +3765,7 @@
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>2938</t>
+          <t>2488</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -3780,7 +3780,7 @@
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>2,54%</t>
+          <t>2,15%</t>
         </is>
       </c>
     </row>
@@ -3803,12 +3803,12 @@
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>3313</t>
+          <t>3276</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>12094</t>
+          <t>11553</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
@@ -3818,12 +3818,12 @@
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>5,91%</t>
+          <t>5,84%</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>21,58%</t>
+          <t>20,61%</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
@@ -3838,12 +3838,12 @@
       </c>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>11047</t>
+          <t>10537</t>
         </is>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>21889</t>
+          <t>21125</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
@@ -3853,12 +3853,12 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>18,49%</t>
+          <t>17,64%</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>36,65%</t>
+          <t>35,37%</t>
         </is>
       </c>
       <c r="Q31" s="2" t="inlineStr">
@@ -3873,12 +3873,12 @@
       </c>
       <c r="S31" s="2" t="inlineStr">
         <is>
-          <t>15626</t>
+          <t>15593</t>
         </is>
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>29271</t>
+          <t>28890</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
@@ -3888,12 +3888,12 @@
       </c>
       <c r="V31" s="2" t="inlineStr">
         <is>
-          <t>13,5%</t>
+          <t>13,47%</t>
         </is>
       </c>
       <c r="W31" s="2" t="inlineStr">
         <is>
-          <t>25,28%</t>
+          <t>24,95%</t>
         </is>
       </c>
     </row>
@@ -3916,12 +3916,12 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>34675</t>
+          <t>34620</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>45469</t>
+          <t>45998</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -3931,12 +3931,12 @@
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>61,86%</t>
+          <t>61,76%</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>81,12%</t>
+          <t>82,06%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -3951,12 +3951,12 @@
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>34091</t>
+          <t>34135</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>44991</t>
+          <t>45587</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -3966,12 +3966,12 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>57,07%</t>
+          <t>57,15%</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>75,32%</t>
+          <t>76,32%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -3986,12 +3986,12 @@
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>72350</t>
+          <t>73126</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>88171</t>
+          <t>88735</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
@@ -4001,12 +4001,12 @@
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>62,49%</t>
+          <t>63,16%</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>76,15%</t>
+          <t>76,64%</t>
         </is>
       </c>
     </row>
@@ -4146,12 +4146,12 @@
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>7799</t>
+          <t>7748</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>18416</t>
+          <t>19634</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
@@ -4161,12 +4161,12 @@
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>6,06%</t>
+          <t>6,02%</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>14,32%</t>
+          <t>15,26%</t>
         </is>
       </c>
       <c r="J34" s="2" t="inlineStr">
@@ -4181,12 +4181,12 @@
       </c>
       <c r="L34" s="2" t="inlineStr">
         <is>
-          <t>5966</t>
+          <t>6499</t>
         </is>
       </c>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t>15844</t>
+          <t>16813</t>
         </is>
       </c>
       <c r="N34" s="2" t="inlineStr">
@@ -4196,12 +4196,12 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>4,4%</t>
+          <t>4,79%</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
         <is>
-          <t>11,68%</t>
+          <t>12,39%</t>
         </is>
       </c>
       <c r="Q34" s="2" t="inlineStr">
@@ -4216,12 +4216,12 @@
       </c>
       <c r="S34" s="2" t="inlineStr">
         <is>
-          <t>16202</t>
+          <t>16962</t>
         </is>
       </c>
       <c r="T34" s="2" t="inlineStr">
         <is>
-          <t>31841</t>
+          <t>32090</t>
         </is>
       </c>
       <c r="U34" s="2" t="inlineStr">
@@ -4231,12 +4231,12 @@
       </c>
       <c r="V34" s="2" t="inlineStr">
         <is>
-          <t>6,13%</t>
+          <t>6,42%</t>
         </is>
       </c>
       <c r="W34" s="2" t="inlineStr">
         <is>
-          <t>12,05%</t>
+          <t>12,14%</t>
         </is>
       </c>
     </row>
@@ -4259,12 +4259,12 @@
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>688</t>
+          <t>686</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>6686</t>
+          <t>6076</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
@@ -4279,7 +4279,7 @@
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>5,2%</t>
+          <t>4,72%</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr">
@@ -4294,12 +4294,12 @@
       </c>
       <c r="L35" s="2" t="inlineStr">
         <is>
-          <t>726</t>
+          <t>1364</t>
         </is>
       </c>
       <c r="M35" s="2" t="inlineStr">
         <is>
-          <t>7425</t>
+          <t>7734</t>
         </is>
       </c>
       <c r="N35" s="2" t="inlineStr">
@@ -4309,12 +4309,12 @@
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>0,53%</t>
+          <t>1,01%</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
         <is>
-          <t>5,47%</t>
+          <t>5,7%</t>
         </is>
       </c>
       <c r="Q35" s="2" t="inlineStr">
@@ -4329,12 +4329,12 @@
       </c>
       <c r="S35" s="2" t="inlineStr">
         <is>
-          <t>2766</t>
+          <t>2809</t>
         </is>
       </c>
       <c r="T35" s="2" t="inlineStr">
         <is>
-          <t>11617</t>
+          <t>11358</t>
         </is>
       </c>
       <c r="U35" s="2" t="inlineStr">
@@ -4344,12 +4344,12 @@
       </c>
       <c r="V35" s="2" t="inlineStr">
         <is>
-          <t>1,05%</t>
+          <t>1,06%</t>
         </is>
       </c>
       <c r="W35" s="2" t="inlineStr">
         <is>
-          <t>4,4%</t>
+          <t>4,3%</t>
         </is>
       </c>
     </row>
@@ -4372,12 +4372,12 @@
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>24622</t>
+          <t>25215</t>
         </is>
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>40378</t>
+          <t>41487</t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr">
@@ -4387,12 +4387,12 @@
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t>19,14%</t>
+          <t>19,6%</t>
         </is>
       </c>
       <c r="I36" s="2" t="inlineStr">
         <is>
-          <t>31,39%</t>
+          <t>32,25%</t>
         </is>
       </c>
       <c r="J36" s="2" t="inlineStr">
@@ -4407,12 +4407,12 @@
       </c>
       <c r="L36" s="2" t="inlineStr">
         <is>
-          <t>36353</t>
+          <t>35495</t>
         </is>
       </c>
       <c r="M36" s="2" t="inlineStr">
         <is>
-          <t>54001</t>
+          <t>53801</t>
         </is>
       </c>
       <c r="N36" s="2" t="inlineStr">
@@ -4422,12 +4422,12 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>26,8%</t>
+          <t>26,17%</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
         <is>
-          <t>39,81%</t>
+          <t>39,66%</t>
         </is>
       </c>
       <c r="Q36" s="2" t="inlineStr">
@@ -4442,12 +4442,12 @@
       </c>
       <c r="S36" s="2" t="inlineStr">
         <is>
-          <t>65858</t>
+          <t>64614</t>
         </is>
       </c>
       <c r="T36" s="2" t="inlineStr">
         <is>
-          <t>90251</t>
+          <t>89218</t>
         </is>
       </c>
       <c r="U36" s="2" t="inlineStr">
@@ -4457,12 +4457,12 @@
       </c>
       <c r="V36" s="2" t="inlineStr">
         <is>
-          <t>24,92%</t>
+          <t>24,45%</t>
         </is>
       </c>
       <c r="W36" s="2" t="inlineStr">
         <is>
-          <t>34,15%</t>
+          <t>33,76%</t>
         </is>
       </c>
     </row>
@@ -4485,12 +4485,12 @@
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>71790</t>
+          <t>71847</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>89209</t>
+          <t>89749</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
@@ -4500,12 +4500,12 @@
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>55,81%</t>
+          <t>55,86%</t>
         </is>
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>69,36%</t>
+          <t>69,78%</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr">
@@ -4520,12 +4520,12 @@
       </c>
       <c r="L37" s="2" t="inlineStr">
         <is>
-          <t>68494</t>
+          <t>68049</t>
         </is>
       </c>
       <c r="M37" s="2" t="inlineStr">
         <is>
-          <t>86521</t>
+          <t>86885</t>
         </is>
       </c>
       <c r="N37" s="2" t="inlineStr">
@@ -4535,12 +4535,12 @@
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>50,49%</t>
+          <t>50,16%</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
         <is>
-          <t>63,78%</t>
+          <t>64,05%</t>
         </is>
       </c>
       <c r="Q37" s="2" t="inlineStr">
@@ -4555,12 +4555,12 @@
       </c>
       <c r="S37" s="2" t="inlineStr">
         <is>
-          <t>143627</t>
+          <t>143937</t>
         </is>
       </c>
       <c r="T37" s="2" t="inlineStr">
         <is>
-          <t>170352</t>
+          <t>171059</t>
         </is>
       </c>
       <c r="U37" s="2" t="inlineStr">
@@ -4570,12 +4570,12 @@
       </c>
       <c r="V37" s="2" t="inlineStr">
         <is>
-          <t>54,35%</t>
+          <t>54,46%</t>
         </is>
       </c>
       <c r="W37" s="2" t="inlineStr">
         <is>
-          <t>64,46%</t>
+          <t>64,73%</t>
         </is>
       </c>
     </row>
@@ -4715,12 +4715,12 @@
       </c>
       <c r="E39" s="2" t="inlineStr">
         <is>
-          <t>18581</t>
+          <t>19084</t>
         </is>
       </c>
       <c r="F39" s="2" t="inlineStr">
         <is>
-          <t>33348</t>
+          <t>33595</t>
         </is>
       </c>
       <c r="G39" s="2" t="inlineStr">
@@ -4730,12 +4730,12 @@
       </c>
       <c r="H39" s="2" t="inlineStr">
         <is>
-          <t>11,77%</t>
+          <t>12,09%</t>
         </is>
       </c>
       <c r="I39" s="2" t="inlineStr">
         <is>
-          <t>21,12%</t>
+          <t>21,28%</t>
         </is>
       </c>
       <c r="J39" s="2" t="inlineStr">
@@ -4750,12 +4750,12 @@
       </c>
       <c r="L39" s="2" t="inlineStr">
         <is>
-          <t>13419</t>
+          <t>14183</t>
         </is>
       </c>
       <c r="M39" s="2" t="inlineStr">
         <is>
-          <t>26605</t>
+          <t>27396</t>
         </is>
       </c>
       <c r="N39" s="2" t="inlineStr">
@@ -4765,12 +4765,12 @@
       </c>
       <c r="O39" s="2" t="inlineStr">
         <is>
-          <t>8,18%</t>
+          <t>8,65%</t>
         </is>
       </c>
       <c r="P39" s="2" t="inlineStr">
         <is>
-          <t>16,22%</t>
+          <t>16,7%</t>
         </is>
       </c>
       <c r="Q39" s="2" t="inlineStr">
@@ -4785,12 +4785,12 @@
       </c>
       <c r="S39" s="2" t="inlineStr">
         <is>
-          <t>35932</t>
+          <t>35273</t>
         </is>
       </c>
       <c r="T39" s="2" t="inlineStr">
         <is>
-          <t>55855</t>
+          <t>56436</t>
         </is>
       </c>
       <c r="U39" s="2" t="inlineStr">
@@ -4800,12 +4800,12 @@
       </c>
       <c r="V39" s="2" t="inlineStr">
         <is>
-          <t>11,16%</t>
+          <t>10,96%</t>
         </is>
       </c>
       <c r="W39" s="2" t="inlineStr">
         <is>
-          <t>17,35%</t>
+          <t>17,53%</t>
         </is>
       </c>
     </row>
@@ -4828,12 +4828,12 @@
       </c>
       <c r="E40" s="2" t="inlineStr">
         <is>
-          <t>632</t>
+          <t>631</t>
         </is>
       </c>
       <c r="F40" s="2" t="inlineStr">
         <is>
-          <t>5100</t>
+          <t>5631</t>
         </is>
       </c>
       <c r="G40" s="2" t="inlineStr">
@@ -4848,42 +4848,42 @@
       </c>
       <c r="I40" s="2" t="inlineStr">
         <is>
+          <t>3,57%</t>
+        </is>
+      </c>
+      <c r="J40" s="2" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="K40" s="2" t="inlineStr">
+        <is>
+          <t>5295</t>
+        </is>
+      </c>
+      <c r="L40" s="2" t="inlineStr">
+        <is>
+          <t>2546</t>
+        </is>
+      </c>
+      <c r="M40" s="2" t="inlineStr">
+        <is>
+          <t>9981</t>
+        </is>
+      </c>
+      <c r="N40" s="2" t="inlineStr">
+        <is>
           <t>3,23%</t>
         </is>
       </c>
-      <c r="J40" s="2" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="K40" s="2" t="inlineStr">
-        <is>
-          <t>5295</t>
-        </is>
-      </c>
-      <c r="L40" s="2" t="inlineStr">
-        <is>
-          <t>2079</t>
-        </is>
-      </c>
-      <c r="M40" s="2" t="inlineStr">
-        <is>
-          <t>10079</t>
-        </is>
-      </c>
-      <c r="N40" s="2" t="inlineStr">
-        <is>
-          <t>3,23%</t>
-        </is>
-      </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>1,27%</t>
+          <t>1,55%</t>
         </is>
       </c>
       <c r="P40" s="2" t="inlineStr">
         <is>
-          <t>6,14%</t>
+          <t>6,08%</t>
         </is>
       </c>
       <c r="Q40" s="2" t="inlineStr">
@@ -4898,12 +4898,12 @@
       </c>
       <c r="S40" s="2" t="inlineStr">
         <is>
-          <t>4048</t>
+          <t>3629</t>
         </is>
       </c>
       <c r="T40" s="2" t="inlineStr">
         <is>
-          <t>12614</t>
+          <t>12554</t>
         </is>
       </c>
       <c r="U40" s="2" t="inlineStr">
@@ -4913,12 +4913,12 @@
       </c>
       <c r="V40" s="2" t="inlineStr">
         <is>
-          <t>1,26%</t>
+          <t>1,13%</t>
         </is>
       </c>
       <c r="W40" s="2" t="inlineStr">
         <is>
-          <t>3,92%</t>
+          <t>3,9%</t>
         </is>
       </c>
     </row>
@@ -4941,12 +4941,12 @@
       </c>
       <c r="E41" s="2" t="inlineStr">
         <is>
-          <t>37423</t>
+          <t>37104</t>
         </is>
       </c>
       <c r="F41" s="2" t="inlineStr">
         <is>
-          <t>55267</t>
+          <t>55114</t>
         </is>
       </c>
       <c r="G41" s="2" t="inlineStr">
@@ -4956,12 +4956,12 @@
       </c>
       <c r="H41" s="2" t="inlineStr">
         <is>
-          <t>23,7%</t>
+          <t>23,5%</t>
         </is>
       </c>
       <c r="I41" s="2" t="inlineStr">
         <is>
-          <t>35,0%</t>
+          <t>34,9%</t>
         </is>
       </c>
       <c r="J41" s="2" t="inlineStr">
@@ -4976,12 +4976,12 @@
       </c>
       <c r="L41" s="2" t="inlineStr">
         <is>
-          <t>29178</t>
+          <t>29968</t>
         </is>
       </c>
       <c r="M41" s="2" t="inlineStr">
         <is>
-          <t>46001</t>
+          <t>47361</t>
         </is>
       </c>
       <c r="N41" s="2" t="inlineStr">
@@ -4991,12 +4991,12 @@
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>17,79%</t>
+          <t>18,27%</t>
         </is>
       </c>
       <c r="P41" s="2" t="inlineStr">
         <is>
-          <t>28,04%</t>
+          <t>28,87%</t>
         </is>
       </c>
       <c r="Q41" s="2" t="inlineStr">
@@ -5011,12 +5011,12 @@
       </c>
       <c r="S41" s="2" t="inlineStr">
         <is>
-          <t>73805</t>
+          <t>73349</t>
         </is>
       </c>
       <c r="T41" s="2" t="inlineStr">
         <is>
-          <t>98102</t>
+          <t>99020</t>
         </is>
       </c>
       <c r="U41" s="2" t="inlineStr">
@@ -5026,12 +5026,12 @@
       </c>
       <c r="V41" s="2" t="inlineStr">
         <is>
-          <t>22,92%</t>
+          <t>22,78%</t>
         </is>
       </c>
       <c r="W41" s="2" t="inlineStr">
         <is>
-          <t>30,47%</t>
+          <t>30,76%</t>
         </is>
       </c>
     </row>
@@ -5054,12 +5054,12 @@
       </c>
       <c r="E42" s="2" t="inlineStr">
         <is>
-          <t>74221</t>
+          <t>75073</t>
         </is>
       </c>
       <c r="F42" s="2" t="inlineStr">
         <is>
-          <t>94412</t>
+          <t>94177</t>
         </is>
       </c>
       <c r="G42" s="2" t="inlineStr">
@@ -5069,12 +5069,12 @@
       </c>
       <c r="H42" s="2" t="inlineStr">
         <is>
-          <t>47,0%</t>
+          <t>47,54%</t>
         </is>
       </c>
       <c r="I42" s="2" t="inlineStr">
         <is>
-          <t>59,79%</t>
+          <t>59,64%</t>
         </is>
       </c>
       <c r="J42" s="2" t="inlineStr">
@@ -5089,12 +5089,12 @@
       </c>
       <c r="L42" s="2" t="inlineStr">
         <is>
-          <t>90924</t>
+          <t>90183</t>
         </is>
       </c>
       <c r="M42" s="2" t="inlineStr">
         <is>
-          <t>110565</t>
+          <t>110260</t>
         </is>
       </c>
       <c r="N42" s="2" t="inlineStr">
@@ -5104,12 +5104,12 @@
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>55,42%</t>
+          <t>54,97%</t>
         </is>
       </c>
       <c r="P42" s="2" t="inlineStr">
         <is>
-          <t>67,39%</t>
+          <t>67,21%</t>
         </is>
       </c>
       <c r="Q42" s="2" t="inlineStr">
@@ -5124,12 +5124,12 @@
       </c>
       <c r="S42" s="2" t="inlineStr">
         <is>
-          <t>169386</t>
+          <t>169427</t>
         </is>
       </c>
       <c r="T42" s="2" t="inlineStr">
         <is>
-          <t>196116</t>
+          <t>198648</t>
         </is>
       </c>
       <c r="U42" s="2" t="inlineStr">
@@ -5139,12 +5139,12 @@
       </c>
       <c r="V42" s="2" t="inlineStr">
         <is>
-          <t>52,61%</t>
+          <t>52,62%</t>
         </is>
       </c>
       <c r="W42" s="2" t="inlineStr">
         <is>
-          <t>60,91%</t>
+          <t>61,7%</t>
         </is>
       </c>
     </row>
@@ -5284,12 +5284,12 @@
       </c>
       <c r="E44" s="2" t="inlineStr">
         <is>
-          <t>65212</t>
+          <t>64989</t>
         </is>
       </c>
       <c r="F44" s="2" t="inlineStr">
         <is>
-          <t>92110</t>
+          <t>91919</t>
         </is>
       </c>
       <c r="G44" s="2" t="inlineStr">
@@ -5299,12 +5299,12 @@
       </c>
       <c r="H44" s="2" t="inlineStr">
         <is>
-          <t>9,6%</t>
+          <t>9,57%</t>
         </is>
       </c>
       <c r="I44" s="2" t="inlineStr">
         <is>
-          <t>13,56%</t>
+          <t>13,54%</t>
         </is>
       </c>
       <c r="J44" s="2" t="inlineStr">
@@ -5319,12 +5319,12 @@
       </c>
       <c r="L44" s="2" t="inlineStr">
         <is>
-          <t>54020</t>
+          <t>54844</t>
         </is>
       </c>
       <c r="M44" s="2" t="inlineStr">
         <is>
-          <t>78123</t>
+          <t>80245</t>
         </is>
       </c>
       <c r="N44" s="2" t="inlineStr">
@@ -5334,12 +5334,12 @@
       </c>
       <c r="O44" s="2" t="inlineStr">
         <is>
-          <t>7,48%</t>
+          <t>7,6%</t>
         </is>
       </c>
       <c r="P44" s="2" t="inlineStr">
         <is>
-          <t>10,82%</t>
+          <t>11,11%</t>
         </is>
       </c>
       <c r="Q44" s="2" t="inlineStr">
@@ -5354,12 +5354,12 @@
       </c>
       <c r="S44" s="2" t="inlineStr">
         <is>
-          <t>126939</t>
+          <t>127448</t>
         </is>
       </c>
       <c r="T44" s="2" t="inlineStr">
         <is>
-          <t>162040</t>
+          <t>163766</t>
         </is>
       </c>
       <c r="U44" s="2" t="inlineStr">
@@ -5369,12 +5369,12 @@
       </c>
       <c r="V44" s="2" t="inlineStr">
         <is>
-          <t>9,06%</t>
+          <t>9,1%</t>
         </is>
       </c>
       <c r="W44" s="2" t="inlineStr">
         <is>
-          <t>11,57%</t>
+          <t>11,69%</t>
         </is>
       </c>
     </row>
@@ -5397,12 +5397,12 @@
       </c>
       <c r="E45" s="2" t="inlineStr">
         <is>
-          <t>4020</t>
+          <t>4445</t>
         </is>
       </c>
       <c r="F45" s="2" t="inlineStr">
         <is>
-          <t>13092</t>
+          <t>13261</t>
         </is>
       </c>
       <c r="G45" s="2" t="inlineStr">
@@ -5412,12 +5412,12 @@
       </c>
       <c r="H45" s="2" t="inlineStr">
         <is>
-          <t>0,59%</t>
+          <t>0,65%</t>
         </is>
       </c>
       <c r="I45" s="2" t="inlineStr">
         <is>
-          <t>1,93%</t>
+          <t>1,95%</t>
         </is>
       </c>
       <c r="J45" s="2" t="inlineStr">
@@ -5432,12 +5432,12 @@
       </c>
       <c r="L45" s="2" t="inlineStr">
         <is>
-          <t>10213</t>
+          <t>10181</t>
         </is>
       </c>
       <c r="M45" s="2" t="inlineStr">
         <is>
-          <t>21978</t>
+          <t>23318</t>
         </is>
       </c>
       <c r="N45" s="2" t="inlineStr">
@@ -5452,7 +5452,7 @@
       </c>
       <c r="P45" s="2" t="inlineStr">
         <is>
-          <t>3,04%</t>
+          <t>3,23%</t>
         </is>
       </c>
       <c r="Q45" s="2" t="inlineStr">
@@ -5467,12 +5467,12 @@
       </c>
       <c r="S45" s="2" t="inlineStr">
         <is>
-          <t>16916</t>
+          <t>16487</t>
         </is>
       </c>
       <c r="T45" s="2" t="inlineStr">
         <is>
-          <t>32073</t>
+          <t>31098</t>
         </is>
       </c>
       <c r="U45" s="2" t="inlineStr">
@@ -5482,12 +5482,12 @@
       </c>
       <c r="V45" s="2" t="inlineStr">
         <is>
-          <t>1,21%</t>
+          <t>1,18%</t>
         </is>
       </c>
       <c r="W45" s="2" t="inlineStr">
         <is>
-          <t>2,29%</t>
+          <t>2,22%</t>
         </is>
       </c>
     </row>
@@ -5510,12 +5510,12 @@
       </c>
       <c r="E46" s="2" t="inlineStr">
         <is>
-          <t>174733</t>
+          <t>175235</t>
         </is>
       </c>
       <c r="F46" s="2" t="inlineStr">
         <is>
-          <t>212872</t>
+          <t>214808</t>
         </is>
       </c>
       <c r="G46" s="2" t="inlineStr">
@@ -5525,12 +5525,12 @@
       </c>
       <c r="H46" s="2" t="inlineStr">
         <is>
-          <t>25,73%</t>
+          <t>25,81%</t>
         </is>
       </c>
       <c r="I46" s="2" t="inlineStr">
         <is>
-          <t>31,35%</t>
+          <t>31,63%</t>
         </is>
       </c>
       <c r="J46" s="2" t="inlineStr">
@@ -5545,12 +5545,12 @@
       </c>
       <c r="L46" s="2" t="inlineStr">
         <is>
-          <t>185003</t>
+          <t>184921</t>
         </is>
       </c>
       <c r="M46" s="2" t="inlineStr">
         <is>
-          <t>222777</t>
+          <t>223767</t>
         </is>
       </c>
       <c r="N46" s="2" t="inlineStr">
@@ -5560,12 +5560,12 @@
       </c>
       <c r="O46" s="2" t="inlineStr">
         <is>
-          <t>25,62%</t>
+          <t>25,61%</t>
         </is>
       </c>
       <c r="P46" s="2" t="inlineStr">
         <is>
-          <t>30,85%</t>
+          <t>30,99%</t>
         </is>
       </c>
       <c r="Q46" s="2" t="inlineStr">
@@ -5580,12 +5580,12 @@
       </c>
       <c r="S46" s="2" t="inlineStr">
         <is>
-          <t>373172</t>
+          <t>372173</t>
         </is>
       </c>
       <c r="T46" s="2" t="inlineStr">
         <is>
-          <t>424209</t>
+          <t>426882</t>
         </is>
       </c>
       <c r="U46" s="2" t="inlineStr">
@@ -5595,12 +5595,12 @@
       </c>
       <c r="V46" s="2" t="inlineStr">
         <is>
-          <t>26,63%</t>
+          <t>26,56%</t>
         </is>
       </c>
       <c r="W46" s="2" t="inlineStr">
         <is>
-          <t>30,28%</t>
+          <t>30,47%</t>
         </is>
       </c>
     </row>
@@ -5623,12 +5623,12 @@
       </c>
       <c r="E47" s="2" t="inlineStr">
         <is>
-          <t>378413</t>
+          <t>376609</t>
         </is>
       </c>
       <c r="F47" s="2" t="inlineStr">
         <is>
-          <t>419881</t>
+          <t>419789</t>
         </is>
       </c>
       <c r="G47" s="2" t="inlineStr">
@@ -5638,12 +5638,12 @@
       </c>
       <c r="H47" s="2" t="inlineStr">
         <is>
-          <t>55,73%</t>
+          <t>55,46%</t>
         </is>
       </c>
       <c r="I47" s="2" t="inlineStr">
         <is>
-          <t>61,83%</t>
+          <t>61,82%</t>
         </is>
       </c>
       <c r="J47" s="2" t="inlineStr">
@@ -5658,12 +5658,12 @@
       </c>
       <c r="L47" s="2" t="inlineStr">
         <is>
-          <t>415162</t>
+          <t>414848</t>
         </is>
       </c>
       <c r="M47" s="2" t="inlineStr">
         <is>
-          <t>457041</t>
+          <t>456953</t>
         </is>
       </c>
       <c r="N47" s="2" t="inlineStr">
@@ -5673,12 +5673,12 @@
       </c>
       <c r="O47" s="2" t="inlineStr">
         <is>
-          <t>57,5%</t>
+          <t>57,46%</t>
         </is>
       </c>
       <c r="P47" s="2" t="inlineStr">
         <is>
-          <t>63,3%</t>
+          <t>63,29%</t>
         </is>
       </c>
       <c r="Q47" s="2" t="inlineStr">
@@ -5693,12 +5693,12 @@
       </c>
       <c r="S47" s="2" t="inlineStr">
         <is>
-          <t>807728</t>
+          <t>804653</t>
         </is>
       </c>
       <c r="T47" s="2" t="inlineStr">
         <is>
-          <t>864873</t>
+          <t>865819</t>
         </is>
       </c>
       <c r="U47" s="2" t="inlineStr">
@@ -5708,12 +5708,12 @@
       </c>
       <c r="V47" s="2" t="inlineStr">
         <is>
-          <t>57,65%</t>
+          <t>57,43%</t>
         </is>
       </c>
       <c r="W47" s="2" t="inlineStr">
         <is>
-          <t>61,73%</t>
+          <t>61,8%</t>
         </is>
       </c>
     </row>
@@ -6089,12 +6089,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>1958</t>
+          <t>1897</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>9006</t>
+          <t>8922</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -6104,12 +6104,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>3,41%</t>
+          <t>3,3%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>15,68%</t>
+          <t>15,54%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -6124,12 +6124,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>4991</t>
+          <t>4620</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>14552</t>
+          <t>14576</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -6139,12 +6139,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>7,7%</t>
+          <t>7,13%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>22,45%</t>
+          <t>22,49%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -6159,12 +6159,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>8654</t>
+          <t>8066</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>20778</t>
+          <t>19548</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -6174,12 +6174,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>7,08%</t>
+          <t>6,6%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>17,0%</t>
+          <t>15,99%</t>
         </is>
       </c>
     </row>
@@ -6207,7 +6207,7 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>4848</t>
+          <t>4905</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -6222,7 +6222,7 @@
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>8,44%</t>
+          <t>8,54%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -6237,12 +6237,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>677</t>
+          <t>775</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>6428</t>
+          <t>6481</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -6252,12 +6252,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>1,04%</t>
+          <t>1,2%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>9,92%</t>
+          <t>10,0%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -6272,12 +6272,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>1825</t>
+          <t>1385</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>8592</t>
+          <t>8783</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -6287,12 +6287,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>1,49%</t>
+          <t>1,13%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>7,03%</t>
+          <t>7,19%</t>
         </is>
       </c>
     </row>
@@ -6315,12 +6315,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>12196</t>
+          <t>11755</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>22844</t>
+          <t>22872</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -6330,12 +6330,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>21,24%</t>
+          <t>20,47%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>39,78%</t>
+          <t>39,83%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -6350,12 +6350,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>14090</t>
+          <t>13483</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>26017</t>
+          <t>26005</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -6365,12 +6365,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>21,74%</t>
+          <t>20,8%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>40,14%</t>
+          <t>40,13%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -6385,12 +6385,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>28887</t>
+          <t>28767</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>44865</t>
+          <t>45844</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -6400,12 +6400,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>23,63%</t>
+          <t>23,53%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>36,7%</t>
+          <t>37,5%</t>
         </is>
       </c>
     </row>
@@ -6428,12 +6428,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>27773</t>
+          <t>28646</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>40157</t>
+          <t>40101</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -6443,12 +6443,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>48,36%</t>
+          <t>49,88%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>69,93%</t>
+          <t>69,83%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -6463,12 +6463,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>26808</t>
+          <t>26414</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>40211</t>
+          <t>40764</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -6478,12 +6478,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>41,37%</t>
+          <t>40,76%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>62,04%</t>
+          <t>62,9%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -6498,12 +6498,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>58794</t>
+          <t>58441</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>76786</t>
+          <t>76623</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -6513,12 +6513,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>48,1%</t>
+          <t>47,81%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>62,82%</t>
+          <t>62,68%</t>
         </is>
       </c>
     </row>
@@ -6658,12 +6658,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>3759</t>
+          <t>3715</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>13156</t>
+          <t>13996</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -6673,12 +6673,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>3,59%</t>
+          <t>3,55%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>12,56%</t>
+          <t>13,37%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -6693,12 +6693,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>6838</t>
+          <t>7523</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>18318</t>
+          <t>19959</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -6708,12 +6708,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>6,15%</t>
+          <t>6,77%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>16,48%</t>
+          <t>17,96%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -6728,12 +6728,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>12492</t>
+          <t>12602</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>27426</t>
+          <t>26377</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -6743,12 +6743,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>5,79%</t>
+          <t>5,84%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>12,7%</t>
+          <t>12,22%</t>
         </is>
       </c>
     </row>
@@ -6776,7 +6776,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>4487</t>
+          <t>3995</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -6791,7 +6791,7 @@
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>4,29%</t>
+          <t>3,82%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -6806,12 +6806,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>625</t>
+          <t>623</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>5409</t>
+          <t>5308</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -6826,7 +6826,7 @@
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>4,87%</t>
+          <t>4,77%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -6841,12 +6841,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>1278</t>
+          <t>1258</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>7823</t>
+          <t>7595</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -6856,12 +6856,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>0,59%</t>
+          <t>0,58%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>3,62%</t>
+          <t>3,52%</t>
         </is>
       </c>
     </row>
@@ -6884,12 +6884,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>19933</t>
+          <t>20454</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>34468</t>
+          <t>34295</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -6899,12 +6899,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>19,04%</t>
+          <t>19,53%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>32,92%</t>
+          <t>32,75%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -6919,12 +6919,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>25237</t>
+          <t>25391</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>39198</t>
+          <t>40730</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -6934,12 +6934,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>22,7%</t>
+          <t>22,84%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>35,26%</t>
+          <t>36,64%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -6954,12 +6954,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>49186</t>
+          <t>48271</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>69848</t>
+          <t>69438</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -6969,12 +6969,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>22,78%</t>
+          <t>22,36%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>32,36%</t>
+          <t>32,17%</t>
         </is>
       </c>
     </row>
@@ -6997,12 +6997,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>61202</t>
+          <t>61110</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>77173</t>
+          <t>76941</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -7012,12 +7012,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>58,45%</t>
+          <t>58,36%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>73,7%</t>
+          <t>73,48%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -7032,12 +7032,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>57014</t>
+          <t>55812</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>73678</t>
+          <t>72849</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -7047,12 +7047,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>51,29%</t>
+          <t>50,21%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>66,28%</t>
+          <t>65,54%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -7067,12 +7067,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>122087</t>
+          <t>123142</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>144961</t>
+          <t>146095</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -7082,12 +7082,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>56,56%</t>
+          <t>57,04%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>67,15%</t>
+          <t>67,68%</t>
         </is>
       </c>
     </row>
@@ -7227,12 +7227,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>793</t>
+          <t>771</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>7038</t>
+          <t>7352</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -7242,12 +7242,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>1,16%</t>
+          <t>1,13%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>10,32%</t>
+          <t>10,78%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -7262,12 +7262,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>1419</t>
+          <t>1413</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>7895</t>
+          <t>7252</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -7277,12 +7277,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>1,99%</t>
+          <t>1,98%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>11,08%</t>
+          <t>10,18%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -7297,12 +7297,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>3491</t>
+          <t>2949</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>11883</t>
+          <t>11634</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -7312,12 +7312,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>2,5%</t>
+          <t>2,12%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>8,52%</t>
+          <t>8,34%</t>
         </is>
       </c>
     </row>
@@ -7380,7 +7380,7 @@
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>4236</t>
+          <t>4279</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -7395,7 +7395,7 @@
       </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t>5,94%</t>
+          <t>6,0%</t>
         </is>
       </c>
       <c r="Q15" s="2" t="inlineStr">
@@ -7415,7 +7415,7 @@
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>4399</t>
+          <t>4884</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -7430,7 +7430,7 @@
       </c>
       <c r="W15" s="2" t="inlineStr">
         <is>
-          <t>3,16%</t>
+          <t>3,5%</t>
         </is>
       </c>
     </row>
@@ -7453,12 +7453,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>9671</t>
+          <t>9500</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>20827</t>
+          <t>21122</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -7468,12 +7468,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>14,19%</t>
+          <t>13,93%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>30,55%</t>
+          <t>30,98%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -7488,12 +7488,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>14161</t>
+          <t>13485</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>26875</t>
+          <t>26119</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -7503,12 +7503,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>19,87%</t>
+          <t>18,93%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>37,72%</t>
+          <t>36,66%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -7523,12 +7523,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>26897</t>
+          <t>26717</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>43398</t>
+          <t>43487</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -7538,12 +7538,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>19,29%</t>
+          <t>19,16%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>31,12%</t>
+          <t>31,19%</t>
         </is>
       </c>
     </row>
@@ -7566,12 +7566,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>44397</t>
+          <t>43872</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>56074</t>
+          <t>56152</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -7581,12 +7581,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>65,12%</t>
+          <t>64,35%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>82,25%</t>
+          <t>82,36%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -7601,12 +7601,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>39408</t>
+          <t>39502</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>52273</t>
+          <t>52903</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -7616,12 +7616,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>55,31%</t>
+          <t>55,44%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>73,36%</t>
+          <t>74,25%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -7636,12 +7636,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>87163</t>
+          <t>86966</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>105180</t>
+          <t>105315</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -7651,12 +7651,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>62,51%</t>
+          <t>62,37%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>75,43%</t>
+          <t>75,53%</t>
         </is>
       </c>
     </row>
@@ -7796,12 +7796,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>1420</t>
+          <t>1419</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>8115</t>
+          <t>8554</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -7811,12 +7811,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>1,83%</t>
+          <t>1,82%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>10,44%</t>
+          <t>11,0%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -7831,12 +7831,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>2128</t>
+          <t>2142</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>10639</t>
+          <t>10415</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -7846,12 +7846,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>2,59%</t>
+          <t>2,6%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>12,94%</t>
+          <t>12,67%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -7866,12 +7866,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>5295</t>
+          <t>5109</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>15678</t>
+          <t>15198</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -7881,12 +7881,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>3,31%</t>
+          <t>3,19%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>9,8%</t>
+          <t>9,5%</t>
         </is>
       </c>
     </row>
@@ -7909,12 +7909,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>1263</t>
+          <t>1125</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>8046</t>
+          <t>7833</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -7924,12 +7924,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>1,62%</t>
+          <t>1,45%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>10,35%</t>
+          <t>10,07%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -7944,12 +7944,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>864</t>
+          <t>682</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>6837</t>
+          <t>6887</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -7959,12 +7959,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>1,05%</t>
+          <t>0,83%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>8,31%</t>
+          <t>8,37%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -7979,12 +7979,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>3144</t>
+          <t>2833</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>11621</t>
+          <t>11001</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -7994,12 +7994,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>1,96%</t>
+          <t>1,77%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>7,26%</t>
+          <t>6,88%</t>
         </is>
       </c>
     </row>
@@ -8022,12 +8022,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>21987</t>
+          <t>21625</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>36214</t>
+          <t>35481</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -8037,12 +8037,12 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>28,28%</t>
+          <t>27,81%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>46,57%</t>
+          <t>45,63%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -8057,12 +8057,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>25136</t>
+          <t>24478</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>40465</t>
+          <t>40344</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -8072,12 +8072,12 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>30,57%</t>
+          <t>29,77%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>49,21%</t>
+          <t>49,06%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -8092,12 +8092,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>49726</t>
+          <t>50689</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>70916</t>
+          <t>71230</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -8107,12 +8107,12 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>31,08%</t>
+          <t>31,68%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>44,32%</t>
+          <t>44,52%</t>
         </is>
       </c>
     </row>
@@ -8135,12 +8135,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>34094</t>
+          <t>34755</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>48603</t>
+          <t>48960</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -8150,12 +8150,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>43,84%</t>
+          <t>44,69%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>62,5%</t>
+          <t>62,96%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -8170,12 +8170,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>33812</t>
+          <t>34283</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>49643</t>
+          <t>50651</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -8185,12 +8185,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>41,12%</t>
+          <t>41,69%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>60,37%</t>
+          <t>61,59%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -8205,12 +8205,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>74001</t>
+          <t>72991</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>95246</t>
+          <t>94240</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -8220,12 +8220,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>46,25%</t>
+          <t>45,62%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>59,53%</t>
+          <t>58,9%</t>
         </is>
       </c>
     </row>
@@ -8365,12 +8365,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>695</t>
+          <t>682</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>7104</t>
+          <t>6589</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -8380,12 +8380,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>1,58%</t>
+          <t>1,55%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>16,18%</t>
+          <t>15,01%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -8400,12 +8400,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>696</t>
+          <t>707</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>6301</t>
+          <t>6639</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -8415,12 +8415,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>1,49%</t>
+          <t>1,51%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>13,48%</t>
+          <t>14,2%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -8435,12 +8435,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>2257</t>
+          <t>2349</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>10340</t>
+          <t>10464</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -8450,12 +8450,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>2,49%</t>
+          <t>2,59%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>11,41%</t>
+          <t>11,54%</t>
         </is>
       </c>
     </row>
@@ -8483,7 +8483,7 @@
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>4801</t>
+          <t>4418</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -8498,7 +8498,7 @@
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>10,94%</t>
+          <t>10,06%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -8553,7 +8553,7 @@
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>4464</t>
+          <t>4469</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -8568,7 +8568,7 @@
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>4,92%</t>
+          <t>4,93%</t>
         </is>
       </c>
     </row>
@@ -8591,12 +8591,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>13041</t>
+          <t>13347</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>24508</t>
+          <t>24076</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -8606,12 +8606,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>29,71%</t>
+          <t>30,4%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>55,83%</t>
+          <t>54,84%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -8626,12 +8626,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>14277</t>
+          <t>14394</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>25418</t>
+          <t>25995</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -8641,12 +8641,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>30,54%</t>
+          <t>30,79%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>54,37%</t>
+          <t>55,6%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -8661,12 +8661,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>29767</t>
+          <t>30361</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>45446</t>
+          <t>46569</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -8676,12 +8676,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>32,84%</t>
+          <t>33,49%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>50,13%</t>
+          <t>51,37%</t>
         </is>
       </c>
     </row>
@@ -8704,12 +8704,12 @@
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>14831</t>
+          <t>14699</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>26882</t>
+          <t>26109</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
@@ -8719,12 +8719,12 @@
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>33,78%</t>
+          <t>33,48%</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>61,23%</t>
+          <t>59,47%</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
@@ -8739,12 +8739,12 @@
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>18933</t>
+          <t>18179</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>29832</t>
+          <t>30395</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
@@ -8754,12 +8754,12 @@
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>40,5%</t>
+          <t>38,88%</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
         <is>
-          <t>63,81%</t>
+          <t>65,01%</t>
         </is>
       </c>
       <c r="Q27" s="2" t="inlineStr">
@@ -8774,12 +8774,12 @@
       </c>
       <c r="S27" s="2" t="inlineStr">
         <is>
-          <t>38171</t>
+          <t>38115</t>
         </is>
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>54626</t>
+          <t>54067</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
@@ -8789,12 +8789,12 @@
       </c>
       <c r="V27" s="2" t="inlineStr">
         <is>
-          <t>42,11%</t>
+          <t>42,04%</t>
         </is>
       </c>
       <c r="W27" s="2" t="inlineStr">
         <is>
-          <t>60,26%</t>
+          <t>59,64%</t>
         </is>
       </c>
     </row>
@@ -8934,12 +8934,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>1211</t>
+          <t>1222</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>7871</t>
+          <t>7748</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -8949,12 +8949,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>2,16%</t>
+          <t>2,18%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>14,06%</t>
+          <t>13,84%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -8969,12 +8969,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>1124</t>
+          <t>1120</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>8394</t>
+          <t>8805</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -8984,12 +8984,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>1,87%</t>
+          <t>1,86%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>13,93%</t>
+          <t>14,61%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -9004,12 +9004,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>3354</t>
+          <t>3366</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>12406</t>
+          <t>13156</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -9019,12 +9019,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>2,89%</t>
+          <t>2,9%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>10,67%</t>
+          <t>11,32%</t>
         </is>
       </c>
     </row>
@@ -9052,7 +9052,7 @@
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>4667</t>
+          <t>4170</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -9067,7 +9067,7 @@
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>8,34%</t>
+          <t>7,45%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -9087,7 +9087,7 @@
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>4255</t>
+          <t>3683</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -9102,7 +9102,7 @@
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>7,06%</t>
+          <t>6,11%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -9117,12 +9117,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>686</t>
+          <t>666</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>6255</t>
+          <t>5868</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -9132,12 +9132,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>0,59%</t>
+          <t>0,57%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>5,38%</t>
+          <t>5,05%</t>
         </is>
       </c>
     </row>
@@ -9160,12 +9160,12 @@
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>12654</t>
+          <t>12677</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>24251</t>
+          <t>24584</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
@@ -9175,12 +9175,12 @@
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>22,6%</t>
+          <t>22,64%</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>43,32%</t>
+          <t>43,91%</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
@@ -9195,12 +9195,12 @@
       </c>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>8116</t>
+          <t>8339</t>
         </is>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>18511</t>
+          <t>18726</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
@@ -9210,12 +9210,12 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>13,47%</t>
+          <t>13,84%</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>30,73%</t>
+          <t>31,08%</t>
         </is>
       </c>
       <c r="Q31" s="2" t="inlineStr">
@@ -9230,12 +9230,12 @@
       </c>
       <c r="S31" s="2" t="inlineStr">
         <is>
-          <t>23767</t>
+          <t>23227</t>
         </is>
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>39110</t>
+          <t>39200</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
@@ -9245,12 +9245,12 @@
       </c>
       <c r="V31" s="2" t="inlineStr">
         <is>
-          <t>20,45%</t>
+          <t>19,98%</t>
         </is>
       </c>
       <c r="W31" s="2" t="inlineStr">
         <is>
-          <t>33,65%</t>
+          <t>33,73%</t>
         </is>
       </c>
     </row>
@@ -9273,12 +9273,12 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>26786</t>
+          <t>26562</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>39093</t>
+          <t>39157</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -9288,12 +9288,12 @@
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>47,84%</t>
+          <t>47,45%</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>69,83%</t>
+          <t>69,94%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -9308,12 +9308,12 @@
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>36764</t>
+          <t>36113</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>48096</t>
+          <t>47934</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -9323,12 +9323,12 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>61,02%</t>
+          <t>59,94%</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>79,83%</t>
+          <t>79,57%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -9343,12 +9343,12 @@
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>67578</t>
+          <t>66911</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>84291</t>
+          <t>84841</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
@@ -9358,12 +9358,12 @@
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>58,14%</t>
+          <t>57,57%</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>72,52%</t>
+          <t>72,99%</t>
         </is>
       </c>
     </row>
@@ -9503,12 +9503,12 @@
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>8440</t>
+          <t>8732</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>20664</t>
+          <t>20521</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
@@ -9518,12 +9518,12 @@
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>6,08%</t>
+          <t>6,29%</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>14,9%</t>
+          <t>14,79%</t>
         </is>
       </c>
       <c r="J34" s="2" t="inlineStr">
@@ -9538,12 +9538,12 @@
       </c>
       <c r="L34" s="2" t="inlineStr">
         <is>
-          <t>6801</t>
+          <t>6477</t>
         </is>
       </c>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t>20072</t>
+          <t>18413</t>
         </is>
       </c>
       <c r="N34" s="2" t="inlineStr">
@@ -9553,12 +9553,12 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>4,67%</t>
+          <t>4,44%</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
         <is>
-          <t>13,77%</t>
+          <t>12,63%</t>
         </is>
       </c>
       <c r="Q34" s="2" t="inlineStr">
@@ -9573,12 +9573,12 @@
       </c>
       <c r="S34" s="2" t="inlineStr">
         <is>
-          <t>17520</t>
+          <t>18194</t>
         </is>
       </c>
       <c r="T34" s="2" t="inlineStr">
         <is>
-          <t>34652</t>
+          <t>35147</t>
         </is>
       </c>
       <c r="U34" s="2" t="inlineStr">
@@ -9588,12 +9588,12 @@
       </c>
       <c r="V34" s="2" t="inlineStr">
         <is>
-          <t>6,16%</t>
+          <t>6,4%</t>
         </is>
       </c>
       <c r="W34" s="2" t="inlineStr">
         <is>
-          <t>12,18%</t>
+          <t>12,36%</t>
         </is>
       </c>
     </row>
@@ -9621,7 +9621,7 @@
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>4147</t>
+          <t>2835</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
@@ -9636,7 +9636,7 @@
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>2,99%</t>
+          <t>2,04%</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr">
@@ -9656,7 +9656,7 @@
       </c>
       <c r="M35" s="2" t="inlineStr">
         <is>
-          <t>4154</t>
+          <t>5507</t>
         </is>
       </c>
       <c r="N35" s="2" t="inlineStr">
@@ -9671,7 +9671,7 @@
       </c>
       <c r="P35" s="2" t="inlineStr">
         <is>
-          <t>2,85%</t>
+          <t>3,78%</t>
         </is>
       </c>
       <c r="Q35" s="2" t="inlineStr">
@@ -9686,12 +9686,12 @@
       </c>
       <c r="S35" s="2" t="inlineStr">
         <is>
-          <t>668</t>
+          <t>667</t>
         </is>
       </c>
       <c r="T35" s="2" t="inlineStr">
         <is>
-          <t>6089</t>
+          <t>5500</t>
         </is>
       </c>
       <c r="U35" s="2" t="inlineStr">
@@ -9706,7 +9706,7 @@
       </c>
       <c r="W35" s="2" t="inlineStr">
         <is>
-          <t>2,14%</t>
+          <t>1,93%</t>
         </is>
       </c>
     </row>
@@ -9729,12 +9729,12 @@
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>24122</t>
+          <t>24620</t>
         </is>
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>40508</t>
+          <t>40820</t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr">
@@ -9744,12 +9744,12 @@
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t>17,39%</t>
+          <t>17,75%</t>
         </is>
       </c>
       <c r="I36" s="2" t="inlineStr">
         <is>
-          <t>29,2%</t>
+          <t>29,43%</t>
         </is>
       </c>
       <c r="J36" s="2" t="inlineStr">
@@ -9764,12 +9764,12 @@
       </c>
       <c r="L36" s="2" t="inlineStr">
         <is>
-          <t>38887</t>
+          <t>37916</t>
         </is>
       </c>
       <c r="M36" s="2" t="inlineStr">
         <is>
-          <t>57233</t>
+          <t>56511</t>
         </is>
       </c>
       <c r="N36" s="2" t="inlineStr">
@@ -9779,12 +9779,12 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>26,68%</t>
+          <t>26,02%</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
         <is>
-          <t>39,27%</t>
+          <t>38,78%</t>
         </is>
       </c>
       <c r="Q36" s="2" t="inlineStr">
@@ -9799,12 +9799,12 @@
       </c>
       <c r="S36" s="2" t="inlineStr">
         <is>
-          <t>67087</t>
+          <t>67006</t>
         </is>
       </c>
       <c r="T36" s="2" t="inlineStr">
         <is>
-          <t>92463</t>
+          <t>93277</t>
         </is>
       </c>
       <c r="U36" s="2" t="inlineStr">
@@ -9814,12 +9814,12 @@
       </c>
       <c r="V36" s="2" t="inlineStr">
         <is>
-          <t>23,58%</t>
+          <t>23,56%</t>
         </is>
       </c>
       <c r="W36" s="2" t="inlineStr">
         <is>
-          <t>32,5%</t>
+          <t>32,79%</t>
         </is>
       </c>
     </row>
@@ -9842,12 +9842,12 @@
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>83348</t>
+          <t>82486</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>101192</t>
+          <t>100616</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
@@ -9857,12 +9857,12 @@
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>60,08%</t>
+          <t>59,46%</t>
         </is>
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>72,95%</t>
+          <t>72,53%</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr">
@@ -9877,12 +9877,12 @@
       </c>
       <c r="L37" s="2" t="inlineStr">
         <is>
-          <t>75312</t>
+          <t>75623</t>
         </is>
       </c>
       <c r="M37" s="2" t="inlineStr">
         <is>
-          <t>94820</t>
+          <t>95043</t>
         </is>
       </c>
       <c r="N37" s="2" t="inlineStr">
@@ -9892,12 +9892,12 @@
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>51,68%</t>
+          <t>51,89%</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
         <is>
-          <t>65,06%</t>
+          <t>65,21%</t>
         </is>
       </c>
       <c r="Q37" s="2" t="inlineStr">
@@ -9912,12 +9912,12 @@
       </c>
       <c r="S37" s="2" t="inlineStr">
         <is>
-          <t>163085</t>
+          <t>162171</t>
         </is>
       </c>
       <c r="T37" s="2" t="inlineStr">
         <is>
-          <t>189786</t>
+          <t>190949</t>
         </is>
       </c>
       <c r="U37" s="2" t="inlineStr">
@@ -9927,12 +9927,12 @@
       </c>
       <c r="V37" s="2" t="inlineStr">
         <is>
-          <t>57,33%</t>
+          <t>57,01%</t>
         </is>
       </c>
       <c r="W37" s="2" t="inlineStr">
         <is>
-          <t>66,72%</t>
+          <t>67,13%</t>
         </is>
       </c>
     </row>
@@ -10072,12 +10072,12 @@
       </c>
       <c r="E39" s="2" t="inlineStr">
         <is>
-          <t>9521</t>
+          <t>9052</t>
         </is>
       </c>
       <c r="F39" s="2" t="inlineStr">
         <is>
-          <t>21192</t>
+          <t>20522</t>
         </is>
       </c>
       <c r="G39" s="2" t="inlineStr">
@@ -10087,12 +10087,12 @@
       </c>
       <c r="H39" s="2" t="inlineStr">
         <is>
-          <t>5,86%</t>
+          <t>5,57%</t>
         </is>
       </c>
       <c r="I39" s="2" t="inlineStr">
         <is>
-          <t>13,04%</t>
+          <t>12,63%</t>
         </is>
       </c>
       <c r="J39" s="2" t="inlineStr">
@@ -10107,12 +10107,12 @@
       </c>
       <c r="L39" s="2" t="inlineStr">
         <is>
-          <t>10119</t>
+          <t>10594</t>
         </is>
       </c>
       <c r="M39" s="2" t="inlineStr">
         <is>
-          <t>23040</t>
+          <t>23374</t>
         </is>
       </c>
       <c r="N39" s="2" t="inlineStr">
@@ -10122,12 +10122,12 @@
       </c>
       <c r="O39" s="2" t="inlineStr">
         <is>
-          <t>5,91%</t>
+          <t>6,18%</t>
         </is>
       </c>
       <c r="P39" s="2" t="inlineStr">
         <is>
-          <t>13,45%</t>
+          <t>13,64%</t>
         </is>
       </c>
       <c r="Q39" s="2" t="inlineStr">
@@ -10142,12 +10142,12 @@
       </c>
       <c r="S39" s="2" t="inlineStr">
         <is>
-          <t>22180</t>
+          <t>22325</t>
         </is>
       </c>
       <c r="T39" s="2" t="inlineStr">
         <is>
-          <t>39678</t>
+          <t>39869</t>
         </is>
       </c>
       <c r="U39" s="2" t="inlineStr">
@@ -10157,12 +10157,12 @@
       </c>
       <c r="V39" s="2" t="inlineStr">
         <is>
-          <t>6,64%</t>
+          <t>6,69%</t>
         </is>
       </c>
       <c r="W39" s="2" t="inlineStr">
         <is>
-          <t>11,88%</t>
+          <t>11,94%</t>
         </is>
       </c>
     </row>
@@ -10185,12 +10185,12 @@
       </c>
       <c r="E40" s="2" t="inlineStr">
         <is>
-          <t>614</t>
+          <t>792</t>
         </is>
       </c>
       <c r="F40" s="2" t="inlineStr">
         <is>
-          <t>7051</t>
+          <t>6498</t>
         </is>
       </c>
       <c r="G40" s="2" t="inlineStr">
@@ -10200,12 +10200,12 @@
       </c>
       <c r="H40" s="2" t="inlineStr">
         <is>
-          <t>0,38%</t>
+          <t>0,49%</t>
         </is>
       </c>
       <c r="I40" s="2" t="inlineStr">
         <is>
-          <t>4,34%</t>
+          <t>4,0%</t>
         </is>
       </c>
       <c r="J40" s="2" t="inlineStr">
@@ -10220,12 +10220,12 @@
       </c>
       <c r="L40" s="2" t="inlineStr">
         <is>
-          <t>1972</t>
+          <t>1890</t>
         </is>
       </c>
       <c r="M40" s="2" t="inlineStr">
         <is>
-          <t>9368</t>
+          <t>8684</t>
         </is>
       </c>
       <c r="N40" s="2" t="inlineStr">
@@ -10235,12 +10235,12 @@
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>1,15%</t>
+          <t>1,1%</t>
         </is>
       </c>
       <c r="P40" s="2" t="inlineStr">
         <is>
-          <t>5,47%</t>
+          <t>5,07%</t>
         </is>
       </c>
       <c r="Q40" s="2" t="inlineStr">
@@ -10255,12 +10255,12 @@
       </c>
       <c r="S40" s="2" t="inlineStr">
         <is>
-          <t>3856</t>
+          <t>3709</t>
         </is>
       </c>
       <c r="T40" s="2" t="inlineStr">
         <is>
-          <t>12244</t>
+          <t>12719</t>
         </is>
       </c>
       <c r="U40" s="2" t="inlineStr">
@@ -10270,12 +10270,12 @@
       </c>
       <c r="V40" s="2" t="inlineStr">
         <is>
-          <t>1,15%</t>
+          <t>1,11%</t>
         </is>
       </c>
       <c r="W40" s="2" t="inlineStr">
         <is>
-          <t>3,67%</t>
+          <t>3,81%</t>
         </is>
       </c>
     </row>
@@ -10298,12 +10298,12 @@
       </c>
       <c r="E41" s="2" t="inlineStr">
         <is>
-          <t>35083</t>
+          <t>34411</t>
         </is>
       </c>
       <c r="F41" s="2" t="inlineStr">
         <is>
-          <t>53256</t>
+          <t>53730</t>
         </is>
       </c>
       <c r="G41" s="2" t="inlineStr">
@@ -10313,12 +10313,12 @@
       </c>
       <c r="H41" s="2" t="inlineStr">
         <is>
-          <t>21,58%</t>
+          <t>21,17%</t>
         </is>
       </c>
       <c r="I41" s="2" t="inlineStr">
         <is>
-          <t>32,76%</t>
+          <t>33,06%</t>
         </is>
       </c>
       <c r="J41" s="2" t="inlineStr">
@@ -10333,12 +10333,12 @@
       </c>
       <c r="L41" s="2" t="inlineStr">
         <is>
-          <t>46921</t>
+          <t>47510</t>
         </is>
       </c>
       <c r="M41" s="2" t="inlineStr">
         <is>
-          <t>67281</t>
+          <t>67271</t>
         </is>
       </c>
       <c r="N41" s="2" t="inlineStr">
@@ -10348,7 +10348,7 @@
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>27,39%</t>
+          <t>27,73%</t>
         </is>
       </c>
       <c r="P41" s="2" t="inlineStr">
@@ -10368,12 +10368,12 @@
       </c>
       <c r="S41" s="2" t="inlineStr">
         <is>
-          <t>87923</t>
+          <t>88143</t>
         </is>
       </c>
       <c r="T41" s="2" t="inlineStr">
         <is>
-          <t>115894</t>
+          <t>115324</t>
         </is>
       </c>
       <c r="U41" s="2" t="inlineStr">
@@ -10383,12 +10383,12 @@
       </c>
       <c r="V41" s="2" t="inlineStr">
         <is>
-          <t>26,34%</t>
+          <t>26,4%</t>
         </is>
       </c>
       <c r="W41" s="2" t="inlineStr">
         <is>
-          <t>34,71%</t>
+          <t>34,54%</t>
         </is>
       </c>
     </row>
@@ -10411,12 +10411,12 @@
       </c>
       <c r="E42" s="2" t="inlineStr">
         <is>
-          <t>91563</t>
+          <t>90777</t>
         </is>
       </c>
       <c r="F42" s="2" t="inlineStr">
         <is>
-          <t>111247</t>
+          <t>110479</t>
         </is>
       </c>
       <c r="G42" s="2" t="inlineStr">
@@ -10426,12 +10426,12 @@
       </c>
       <c r="H42" s="2" t="inlineStr">
         <is>
-          <t>56,33%</t>
+          <t>55,85%</t>
         </is>
       </c>
       <c r="I42" s="2" t="inlineStr">
         <is>
-          <t>68,44%</t>
+          <t>67,97%</t>
         </is>
       </c>
       <c r="J42" s="2" t="inlineStr">
@@ -10446,12 +10446,12 @@
       </c>
       <c r="L42" s="2" t="inlineStr">
         <is>
-          <t>83420</t>
+          <t>82585</t>
         </is>
       </c>
       <c r="M42" s="2" t="inlineStr">
         <is>
-          <t>103676</t>
+          <t>103158</t>
         </is>
       </c>
       <c r="N42" s="2" t="inlineStr">
@@ -10461,12 +10461,12 @@
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>48,69%</t>
+          <t>48,21%</t>
         </is>
       </c>
       <c r="P42" s="2" t="inlineStr">
         <is>
-          <t>60,52%</t>
+          <t>60,22%</t>
         </is>
       </c>
       <c r="Q42" s="2" t="inlineStr">
@@ -10481,12 +10481,12 @@
       </c>
       <c r="S42" s="2" t="inlineStr">
         <is>
-          <t>179048</t>
+          <t>179711</t>
         </is>
       </c>
       <c r="T42" s="2" t="inlineStr">
         <is>
-          <t>208869</t>
+          <t>207927</t>
         </is>
       </c>
       <c r="U42" s="2" t="inlineStr">
@@ -10496,12 +10496,12 @@
       </c>
       <c r="V42" s="2" t="inlineStr">
         <is>
-          <t>53,63%</t>
+          <t>53,83%</t>
         </is>
       </c>
       <c r="W42" s="2" t="inlineStr">
         <is>
-          <t>62,56%</t>
+          <t>62,28%</t>
         </is>
       </c>
     </row>
@@ -10641,12 +10641,12 @@
       </c>
       <c r="E44" s="2" t="inlineStr">
         <is>
-          <t>44177</t>
+          <t>44080</t>
         </is>
       </c>
       <c r="F44" s="2" t="inlineStr">
         <is>
-          <t>67485</t>
+          <t>68015</t>
         </is>
       </c>
       <c r="G44" s="2" t="inlineStr">
@@ -10656,12 +10656,12 @@
       </c>
       <c r="H44" s="2" t="inlineStr">
         <is>
-          <t>6,23%</t>
+          <t>6,22%</t>
         </is>
       </c>
       <c r="I44" s="2" t="inlineStr">
         <is>
-          <t>9,52%</t>
+          <t>9,59%</t>
         </is>
       </c>
       <c r="J44" s="2" t="inlineStr">
@@ -10676,12 +10676,12 @@
       </c>
       <c r="L44" s="2" t="inlineStr">
         <is>
-          <t>51021</t>
+          <t>51175</t>
         </is>
       </c>
       <c r="M44" s="2" t="inlineStr">
         <is>
-          <t>78783</t>
+          <t>77619</t>
         </is>
       </c>
       <c r="N44" s="2" t="inlineStr">
@@ -10691,12 +10691,12 @@
       </c>
       <c r="O44" s="2" t="inlineStr">
         <is>
-          <t>6,77%</t>
+          <t>6,79%</t>
         </is>
       </c>
       <c r="P44" s="2" t="inlineStr">
         <is>
-          <t>10,46%</t>
+          <t>10,3%</t>
         </is>
       </c>
       <c r="Q44" s="2" t="inlineStr">
@@ -10711,12 +10711,12 @@
       </c>
       <c r="S44" s="2" t="inlineStr">
         <is>
-          <t>99098</t>
+          <t>101921</t>
         </is>
       </c>
       <c r="T44" s="2" t="inlineStr">
         <is>
-          <t>134250</t>
+          <t>137613</t>
         </is>
       </c>
       <c r="U44" s="2" t="inlineStr">
@@ -10726,12 +10726,12 @@
       </c>
       <c r="V44" s="2" t="inlineStr">
         <is>
-          <t>6,77%</t>
+          <t>6,97%</t>
         </is>
       </c>
       <c r="W44" s="2" t="inlineStr">
         <is>
-          <t>9,18%</t>
+          <t>9,41%</t>
         </is>
       </c>
     </row>
@@ -10754,12 +10754,12 @@
       </c>
       <c r="E45" s="2" t="inlineStr">
         <is>
-          <t>7256</t>
+          <t>7528</t>
         </is>
       </c>
       <c r="F45" s="2" t="inlineStr">
         <is>
-          <t>18459</t>
+          <t>19222</t>
         </is>
       </c>
       <c r="G45" s="2" t="inlineStr">
@@ -10769,12 +10769,12 @@
       </c>
       <c r="H45" s="2" t="inlineStr">
         <is>
-          <t>1,02%</t>
+          <t>1,06%</t>
         </is>
       </c>
       <c r="I45" s="2" t="inlineStr">
         <is>
-          <t>2,6%</t>
+          <t>2,71%</t>
         </is>
       </c>
       <c r="J45" s="2" t="inlineStr">
@@ -10789,12 +10789,12 @@
       </c>
       <c r="L45" s="2" t="inlineStr">
         <is>
-          <t>10207</t>
+          <t>10530</t>
         </is>
       </c>
       <c r="M45" s="2" t="inlineStr">
         <is>
-          <t>23599</t>
+          <t>22707</t>
         </is>
       </c>
       <c r="N45" s="2" t="inlineStr">
@@ -10804,12 +10804,12 @@
       </c>
       <c r="O45" s="2" t="inlineStr">
         <is>
-          <t>1,35%</t>
+          <t>1,4%</t>
         </is>
       </c>
       <c r="P45" s="2" t="inlineStr">
         <is>
-          <t>3,13%</t>
+          <t>3,01%</t>
         </is>
       </c>
       <c r="Q45" s="2" t="inlineStr">
@@ -10824,12 +10824,12 @@
       </c>
       <c r="S45" s="2" t="inlineStr">
         <is>
-          <t>20589</t>
+          <t>20610</t>
         </is>
       </c>
       <c r="T45" s="2" t="inlineStr">
         <is>
-          <t>37227</t>
+          <t>37372</t>
         </is>
       </c>
       <c r="U45" s="2" t="inlineStr">
@@ -10867,12 +10867,12 @@
       </c>
       <c r="E46" s="2" t="inlineStr">
         <is>
-          <t>178892</t>
+          <t>179692</t>
         </is>
       </c>
       <c r="F46" s="2" t="inlineStr">
         <is>
-          <t>218806</t>
+          <t>218660</t>
         </is>
       </c>
       <c r="G46" s="2" t="inlineStr">
@@ -10882,12 +10882,12 @@
       </c>
       <c r="H46" s="2" t="inlineStr">
         <is>
-          <t>25,22%</t>
+          <t>25,34%</t>
         </is>
       </c>
       <c r="I46" s="2" t="inlineStr">
         <is>
-          <t>30,85%</t>
+          <t>30,83%</t>
         </is>
       </c>
       <c r="J46" s="2" t="inlineStr">
@@ -10902,12 +10902,12 @@
       </c>
       <c r="L46" s="2" t="inlineStr">
         <is>
-          <t>219488</t>
+          <t>220119</t>
         </is>
       </c>
       <c r="M46" s="2" t="inlineStr">
         <is>
-          <t>262649</t>
+          <t>263456</t>
         </is>
       </c>
       <c r="N46" s="2" t="inlineStr">
@@ -10917,12 +10917,12 @@
       </c>
       <c r="O46" s="2" t="inlineStr">
         <is>
-          <t>29,13%</t>
+          <t>29,21%</t>
         </is>
       </c>
       <c r="P46" s="2" t="inlineStr">
         <is>
-          <t>34,86%</t>
+          <t>34,96%</t>
         </is>
       </c>
       <c r="Q46" s="2" t="inlineStr">
@@ -10937,12 +10937,12 @@
       </c>
       <c r="S46" s="2" t="inlineStr">
         <is>
-          <t>411370</t>
+          <t>412275</t>
         </is>
       </c>
       <c r="T46" s="2" t="inlineStr">
         <is>
-          <t>467524</t>
+          <t>470297</t>
         </is>
       </c>
       <c r="U46" s="2" t="inlineStr">
@@ -10952,12 +10952,12 @@
       </c>
       <c r="V46" s="2" t="inlineStr">
         <is>
-          <t>28,12%</t>
+          <t>28,19%</t>
         </is>
       </c>
       <c r="W46" s="2" t="inlineStr">
         <is>
-          <t>31,96%</t>
+          <t>32,15%</t>
         </is>
       </c>
     </row>
@@ -10980,12 +10980,12 @@
       </c>
       <c r="E47" s="2" t="inlineStr">
         <is>
-          <t>423095</t>
+          <t>422645</t>
         </is>
       </c>
       <c r="F47" s="2" t="inlineStr">
         <is>
-          <t>465248</t>
+          <t>464125</t>
         </is>
       </c>
       <c r="G47" s="2" t="inlineStr">
@@ -10995,12 +10995,12 @@
       </c>
       <c r="H47" s="2" t="inlineStr">
         <is>
-          <t>59,66%</t>
+          <t>59,59%</t>
         </is>
       </c>
       <c r="I47" s="2" t="inlineStr">
         <is>
-          <t>65,6%</t>
+          <t>65,44%</t>
         </is>
       </c>
       <c r="J47" s="2" t="inlineStr">
@@ -11015,12 +11015,12 @@
       </c>
       <c r="L47" s="2" t="inlineStr">
         <is>
-          <t>409879</t>
+          <t>410542</t>
         </is>
       </c>
       <c r="M47" s="2" t="inlineStr">
         <is>
-          <t>454816</t>
+          <t>455587</t>
         </is>
       </c>
       <c r="N47" s="2" t="inlineStr">
@@ -11030,12 +11030,12 @@
       </c>
       <c r="O47" s="2" t="inlineStr">
         <is>
-          <t>54,4%</t>
+          <t>54,48%</t>
         </is>
       </c>
       <c r="P47" s="2" t="inlineStr">
         <is>
-          <t>60,36%</t>
+          <t>60,46%</t>
         </is>
       </c>
       <c r="Q47" s="2" t="inlineStr">
@@ -11050,12 +11050,12 @@
       </c>
       <c r="S47" s="2" t="inlineStr">
         <is>
-          <t>846905</t>
+          <t>846657</t>
         </is>
       </c>
       <c r="T47" s="2" t="inlineStr">
         <is>
-          <t>908413</t>
+          <t>909090</t>
         </is>
       </c>
       <c r="U47" s="2" t="inlineStr">
@@ -11065,12 +11065,12 @@
       </c>
       <c r="V47" s="2" t="inlineStr">
         <is>
-          <t>57,9%</t>
+          <t>57,88%</t>
         </is>
       </c>
       <c r="W47" s="2" t="inlineStr">
         <is>
-          <t>62,1%</t>
+          <t>62,15%</t>
         </is>
       </c>
     </row>
@@ -11446,12 +11446,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>1552</t>
+          <t>1525</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>8352</t>
+          <t>8003</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -11461,12 +11461,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>2,75%</t>
+          <t>2,7%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>14,79%</t>
+          <t>14,17%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -11481,12 +11481,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>12878</t>
+          <t>12383</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>24627</t>
+          <t>24418</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -11496,12 +11496,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>19,98%</t>
+          <t>19,21%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>38,2%</t>
+          <t>37,88%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -11516,12 +11516,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>15525</t>
+          <t>15293</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>29465</t>
+          <t>29104</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -11531,12 +11531,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>12,84%</t>
+          <t>12,65%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>24,37%</t>
+          <t>24,07%</t>
         </is>
       </c>
     </row>
@@ -11559,12 +11559,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>1666</t>
+          <t>1764</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>8964</t>
+          <t>8927</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -11574,12 +11574,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>2,95%</t>
+          <t>3,12%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>15,88%</t>
+          <t>15,81%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -11599,7 +11599,7 @@
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>6067</t>
+          <t>6922</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -11614,7 +11614,7 @@
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>9,41%</t>
+          <t>10,74%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -11629,12 +11629,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>3486</t>
+          <t>3481</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>12541</t>
+          <t>12577</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -11649,7 +11649,7 @@
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>10,37%</t>
+          <t>10,4%</t>
         </is>
       </c>
     </row>
@@ -11672,12 +11672,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>9970</t>
+          <t>9849</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>19283</t>
+          <t>19977</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -11687,12 +11687,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>17,66%</t>
+          <t>17,44%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>34,15%</t>
+          <t>35,38%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -11707,12 +11707,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>11392</t>
+          <t>11299</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>22309</t>
+          <t>21980</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -11722,12 +11722,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>17,67%</t>
+          <t>17,53%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>34,61%</t>
+          <t>34,1%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -11742,12 +11742,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>23353</t>
+          <t>24143</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>38454</t>
+          <t>38785</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -11757,12 +11757,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>19,31%</t>
+          <t>19,96%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>31,8%</t>
+          <t>32,07%</t>
         </is>
       </c>
     </row>
@@ -11785,12 +11785,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>28485</t>
+          <t>27586</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>39665</t>
+          <t>39346</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -11800,12 +11800,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>50,44%</t>
+          <t>48,85%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>70,24%</t>
+          <t>69,68%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -11820,12 +11820,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>21221</t>
+          <t>21388</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>33955</t>
+          <t>34726</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -11835,12 +11835,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>32,92%</t>
+          <t>33,18%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>52,67%</t>
+          <t>53,87%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -11855,12 +11855,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>51969</t>
+          <t>52704</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>70504</t>
+          <t>69957</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -11870,12 +11870,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>42,97%</t>
+          <t>43,58%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>58,3%</t>
+          <t>57,85%</t>
         </is>
       </c>
     </row>
@@ -12015,12 +12015,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>5440</t>
+          <t>5164</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>14619</t>
+          <t>14808</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -12030,12 +12030,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>5,28%</t>
+          <t>5,01%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>14,18%</t>
+          <t>14,36%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -12050,12 +12050,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>5567</t>
+          <t>5543</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>15764</t>
+          <t>15881</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -12065,12 +12065,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>5,05%</t>
+          <t>5,03%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>14,29%</t>
+          <t>14,4%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -12085,12 +12085,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>12985</t>
+          <t>13253</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>26941</t>
+          <t>27477</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -12100,12 +12100,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>6,09%</t>
+          <t>6,21%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>12,63%</t>
+          <t>12,88%</t>
         </is>
       </c>
     </row>
@@ -12133,7 +12133,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>3543</t>
+          <t>3316</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -12148,7 +12148,7 @@
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>3,44%</t>
+          <t>3,22%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -12168,7 +12168,7 @@
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>3661</t>
+          <t>4314</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -12183,7 +12183,7 @@
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>3,32%</t>
+          <t>3,91%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -12203,7 +12203,7 @@
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>4933</t>
+          <t>5541</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -12218,7 +12218,7 @@
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>2,31%</t>
+          <t>2,6%</t>
         </is>
       </c>
     </row>
@@ -12241,12 +12241,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>15537</t>
+          <t>15106</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>28656</t>
+          <t>28419</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -12256,12 +12256,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>15,07%</t>
+          <t>14,65%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>27,8%</t>
+          <t>27,57%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -12276,12 +12276,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>13214</t>
+          <t>13303</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>27047</t>
+          <t>25871</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -12291,12 +12291,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>11,98%</t>
+          <t>12,06%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>24,53%</t>
+          <t>23,46%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -12311,12 +12311,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>31331</t>
+          <t>31493</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>49589</t>
+          <t>48740</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -12326,12 +12326,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>14,68%</t>
+          <t>14,76%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>23,24%</t>
+          <t>22,84%</t>
         </is>
       </c>
     </row>
@@ -12354,12 +12354,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>64664</t>
+          <t>64546</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>79128</t>
+          <t>78728</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -12369,12 +12369,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>62,72%</t>
+          <t>62,61%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>76,76%</t>
+          <t>76,37%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -12389,12 +12389,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>71906</t>
+          <t>72007</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>87473</t>
+          <t>86864</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -12404,12 +12404,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>65,2%</t>
+          <t>65,29%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>79,32%</t>
+          <t>78,77%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -12424,12 +12424,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>141915</t>
+          <t>141343</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>162207</t>
+          <t>162383</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -12439,12 +12439,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>66,51%</t>
+          <t>66,24%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>76,02%</t>
+          <t>76,1%</t>
         </is>
       </c>
     </row>
@@ -12584,12 +12584,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>2167</t>
+          <t>2251</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>10310</t>
+          <t>10366</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -12599,12 +12599,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>3,24%</t>
+          <t>3,37%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>15,43%</t>
+          <t>15,51%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -12619,12 +12619,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>1636</t>
+          <t>1721</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>9697</t>
+          <t>9704</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -12634,12 +12634,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>2,34%</t>
+          <t>2,46%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>13,87%</t>
+          <t>13,88%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -12654,12 +12654,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>5450</t>
+          <t>5195</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>17176</t>
+          <t>15748</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -12669,12 +12669,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>3,99%</t>
+          <t>3,8%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>12,56%</t>
+          <t>11,52%</t>
         </is>
       </c>
     </row>
@@ -12702,7 +12702,7 @@
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>4901</t>
+          <t>5595</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -12717,7 +12717,7 @@
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>7,33%</t>
+          <t>8,37%</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
@@ -12737,7 +12737,7 @@
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>2994</t>
+          <t>3256</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -12752,7 +12752,7 @@
       </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t>4,28%</t>
+          <t>4,66%</t>
         </is>
       </c>
       <c r="Q15" s="2" t="inlineStr">
@@ -12767,12 +12767,12 @@
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>656</t>
+          <t>649</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>6132</t>
+          <t>5841</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -12782,12 +12782,12 @@
       </c>
       <c r="V15" s="2" t="inlineStr">
         <is>
-          <t>0,48%</t>
+          <t>0,47%</t>
         </is>
       </c>
       <c r="W15" s="2" t="inlineStr">
         <is>
-          <t>4,48%</t>
+          <t>4,27%</t>
         </is>
       </c>
     </row>
@@ -12810,12 +12810,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>13656</t>
+          <t>14031</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>26171</t>
+          <t>26834</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -12825,12 +12825,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>20,43%</t>
+          <t>21,0%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>39,16%</t>
+          <t>40,15%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -12845,12 +12845,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>13101</t>
+          <t>13023</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>25142</t>
+          <t>25294</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -12860,12 +12860,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>18,74%</t>
+          <t>18,63%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>35,97%</t>
+          <t>36,18%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -12880,12 +12880,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>31011</t>
+          <t>30523</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>48872</t>
+          <t>48513</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -12895,12 +12895,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>22,68%</t>
+          <t>22,32%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>35,74%</t>
+          <t>35,48%</t>
         </is>
       </c>
     </row>
@@ -12923,12 +12923,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>32765</t>
+          <t>32998</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>46436</t>
+          <t>47085</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -12938,12 +12938,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>49,03%</t>
+          <t>49,38%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>69,48%</t>
+          <t>70,45%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -12958,12 +12958,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>39230</t>
+          <t>38825</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>51968</t>
+          <t>51920</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -12973,12 +12973,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>56,12%</t>
+          <t>55,54%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>74,34%</t>
+          <t>74,27%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -12993,12 +12993,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>74492</t>
+          <t>75203</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>94297</t>
+          <t>94407</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -13008,12 +13008,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>54,48%</t>
+          <t>55,0%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>68,96%</t>
+          <t>69,04%</t>
         </is>
       </c>
     </row>
@@ -13153,12 +13153,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>6694</t>
+          <t>6128</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>16766</t>
+          <t>16751</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -13168,12 +13168,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>8,78%</t>
+          <t>8,04%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>21,99%</t>
+          <t>21,97%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -13188,12 +13188,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>3733</t>
+          <t>3748</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>13452</t>
+          <t>13026</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -13203,12 +13203,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>4,6%</t>
+          <t>4,62%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>16,57%</t>
+          <t>16,05%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -13223,12 +13223,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>12140</t>
+          <t>12449</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>26048</t>
+          <t>26229</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -13238,12 +13238,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>7,71%</t>
+          <t>7,91%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>16,55%</t>
+          <t>16,66%</t>
         </is>
       </c>
     </row>
@@ -13266,12 +13266,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>570</t>
+          <t>586</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>5531</t>
+          <t>5594</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -13281,12 +13281,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>0,75%</t>
+          <t>0,77%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>7,25%</t>
+          <t>7,34%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -13306,7 +13306,7 @@
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>4977</t>
+          <t>4370</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -13321,7 +13321,7 @@
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>6,13%</t>
+          <t>5,38%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -13336,12 +13336,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>1313</t>
+          <t>1719</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>7567</t>
+          <t>7759</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -13351,12 +13351,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>0,83%</t>
+          <t>1,09%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>4,81%</t>
+          <t>4,93%</t>
         </is>
       </c>
     </row>
@@ -13379,12 +13379,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>16758</t>
+          <t>16160</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>30193</t>
+          <t>29451</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -13394,12 +13394,12 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>21,98%</t>
+          <t>21,19%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>39,6%</t>
+          <t>38,63%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -13414,12 +13414,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>15227</t>
+          <t>15701</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>29259</t>
+          <t>29539</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -13429,12 +13429,12 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>18,76%</t>
+          <t>19,34%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>36,04%</t>
+          <t>36,39%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -13449,12 +13449,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>35341</t>
+          <t>34992</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>53960</t>
+          <t>52939</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -13464,12 +13464,12 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>22,45%</t>
+          <t>22,23%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>34,28%</t>
+          <t>33,63%</t>
         </is>
       </c>
     </row>
@@ -13492,12 +13492,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>33159</t>
+          <t>33038</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>47514</t>
+          <t>47370</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -13507,12 +13507,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>43,49%</t>
+          <t>43,33%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>62,32%</t>
+          <t>62,13%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -13527,12 +13527,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>43274</t>
+          <t>43064</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>57696</t>
+          <t>58163</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -13542,12 +13542,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>53,3%</t>
+          <t>53,04%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>71,07%</t>
+          <t>71,64%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -13562,12 +13562,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>80952</t>
+          <t>81471</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>101255</t>
+          <t>101904</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -13577,12 +13577,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>51,42%</t>
+          <t>51,75%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>64,32%</t>
+          <t>64,73%</t>
         </is>
       </c>
     </row>
@@ -13722,12 +13722,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>615</t>
+          <t>624</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>6199</t>
+          <t>5783</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -13737,12 +13737,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>1,42%</t>
+          <t>1,44%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>14,27%</t>
+          <t>13,31%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -13757,12 +13757,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>1762</t>
+          <t>1810</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>8634</t>
+          <t>9080</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -13772,12 +13772,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>3,8%</t>
+          <t>3,91%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>18,63%</t>
+          <t>19,59%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -13792,12 +13792,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>3057</t>
+          <t>3060</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>11234</t>
+          <t>10833</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -13812,7 +13812,7 @@
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>12,51%</t>
+          <t>12,07%</t>
         </is>
       </c>
     </row>
@@ -13953,7 +13953,7 @@
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>4912</t>
+          <t>5327</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -13968,7 +13968,7 @@
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>11,31%</t>
+          <t>12,26%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -13988,7 +13988,7 @@
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>4897</t>
+          <t>4787</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -14003,7 +14003,7 @@
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>10,56%</t>
+          <t>10,33%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -14018,12 +14018,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>1183</t>
+          <t>1144</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>6747</t>
+          <t>7237</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -14033,12 +14033,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>1,32%</t>
+          <t>1,27%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>7,51%</t>
+          <t>8,06%</t>
         </is>
       </c>
     </row>
@@ -14061,12 +14061,12 @@
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>35534</t>
+          <t>35981</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>42007</t>
+          <t>42192</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
@@ -14076,12 +14076,12 @@
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>81,8%</t>
+          <t>82,83%</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>96,71%</t>
+          <t>97,13%</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
@@ -14096,12 +14096,12 @@
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>35587</t>
+          <t>35563</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>43300</t>
+          <t>43341</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
@@ -14111,12 +14111,12 @@
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>76,78%</t>
+          <t>76,73%</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
         <is>
-          <t>93,42%</t>
+          <t>93,51%</t>
         </is>
       </c>
       <c r="Q27" s="2" t="inlineStr">
@@ -14131,12 +14131,12 @@
       </c>
       <c r="S27" s="2" t="inlineStr">
         <is>
-          <t>75044</t>
+          <t>74277</t>
         </is>
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>84293</t>
+          <t>84261</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
@@ -14146,12 +14146,12 @@
       </c>
       <c r="V27" s="2" t="inlineStr">
         <is>
-          <t>83,58%</t>
+          <t>82,73%</t>
         </is>
       </c>
       <c r="W27" s="2" t="inlineStr">
         <is>
-          <t>93,88%</t>
+          <t>93,84%</t>
         </is>
       </c>
     </row>
@@ -14296,7 +14296,7 @@
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>5230</t>
+          <t>4857</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -14311,7 +14311,7 @@
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>9,76%</t>
+          <t>9,06%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -14326,12 +14326,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>699</t>
+          <t>714</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>6453</t>
+          <t>7361</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -14341,12 +14341,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>1,21%</t>
+          <t>1,24%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>11,18%</t>
+          <t>12,75%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -14361,12 +14361,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>1400</t>
+          <t>1418</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>7980</t>
+          <t>8437</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -14376,12 +14376,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>1,26%</t>
+          <t>1,27%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>7,17%</t>
+          <t>7,58%</t>
         </is>
       </c>
     </row>
@@ -14404,12 +14404,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>749</t>
+          <t>753</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>7553</t>
+          <t>7919</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -14419,12 +14419,12 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>1,4%</t>
+          <t>1,41%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>14,09%</t>
+          <t>14,78%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -14439,12 +14439,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>748</t>
+          <t>737</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>7294</t>
+          <t>6905</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -14454,12 +14454,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>1,29%</t>
+          <t>1,28%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>12,63%</t>
+          <t>11,96%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -14474,12 +14474,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>2610</t>
+          <t>2199</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>12007</t>
+          <t>11426</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -14489,12 +14489,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>2,34%</t>
+          <t>1,97%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>10,78%</t>
+          <t>10,26%</t>
         </is>
       </c>
     </row>
@@ -14517,12 +14517,12 @@
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>6750</t>
+          <t>6673</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>15893</t>
+          <t>16446</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
@@ -14532,12 +14532,12 @@
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>12,59%</t>
+          <t>12,45%</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>29,66%</t>
+          <t>30,69%</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
@@ -14552,12 +14552,12 @@
       </c>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>11904</t>
+          <t>11827</t>
         </is>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>23745</t>
+          <t>24365</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
@@ -14567,12 +14567,12 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>20,62%</t>
+          <t>20,48%</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>41,13%</t>
+          <t>42,2%</t>
         </is>
       </c>
       <c r="Q31" s="2" t="inlineStr">
@@ -14587,12 +14587,12 @@
       </c>
       <c r="S31" s="2" t="inlineStr">
         <is>
-          <t>20862</t>
+          <t>21188</t>
         </is>
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>36397</t>
+          <t>36364</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
@@ -14602,12 +14602,12 @@
       </c>
       <c r="V31" s="2" t="inlineStr">
         <is>
-          <t>18,74%</t>
+          <t>19,03%</t>
         </is>
       </c>
       <c r="W31" s="2" t="inlineStr">
         <is>
-          <t>32,69%</t>
+          <t>32,66%</t>
         </is>
       </c>
     </row>
@@ -14630,12 +14630,12 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>31704</t>
+          <t>32173</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>42933</t>
+          <t>43381</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -14645,12 +14645,12 @@
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>59,16%</t>
+          <t>60,03%</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>80,11%</t>
+          <t>80,95%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -14665,12 +14665,12 @@
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>28789</t>
+          <t>28484</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>41678</t>
+          <t>41466</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -14680,12 +14680,12 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>49,86%</t>
+          <t>49,33%</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>72,18%</t>
+          <t>71,82%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -14700,12 +14700,12 @@
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>65116</t>
+          <t>64636</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>81338</t>
+          <t>81765</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
@@ -14715,12 +14715,12 @@
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>58,49%</t>
+          <t>58,06%</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>73,06%</t>
+          <t>73,44%</t>
         </is>
       </c>
     </row>
@@ -14860,12 +14860,12 @@
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>9128</t>
+          <t>9522</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>20784</t>
+          <t>20445</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
@@ -14875,12 +14875,12 @@
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>6,64%</t>
+          <t>6,93%</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>15,13%</t>
+          <t>14,88%</t>
         </is>
       </c>
       <c r="J34" s="2" t="inlineStr">
@@ -14895,12 +14895,12 @@
       </c>
       <c r="L34" s="2" t="inlineStr">
         <is>
-          <t>7307</t>
+          <t>7256</t>
         </is>
       </c>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t>17661</t>
+          <t>17993</t>
         </is>
       </c>
       <c r="N34" s="2" t="inlineStr">
@@ -14910,12 +14910,12 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>5,1%</t>
+          <t>5,06%</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
         <is>
-          <t>12,32%</t>
+          <t>12,55%</t>
         </is>
       </c>
       <c r="Q34" s="2" t="inlineStr">
@@ -14930,12 +14930,12 @@
       </c>
       <c r="S34" s="2" t="inlineStr">
         <is>
-          <t>19162</t>
+          <t>18947</t>
         </is>
       </c>
       <c r="T34" s="2" t="inlineStr">
         <is>
-          <t>34123</t>
+          <t>34413</t>
         </is>
       </c>
       <c r="U34" s="2" t="inlineStr">
@@ -14945,12 +14945,12 @@
       </c>
       <c r="V34" s="2" t="inlineStr">
         <is>
-          <t>6,82%</t>
+          <t>6,75%</t>
         </is>
       </c>
       <c r="W34" s="2" t="inlineStr">
         <is>
-          <t>12,15%</t>
+          <t>12,26%</t>
         </is>
       </c>
     </row>
@@ -14978,7 +14978,7 @@
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>6468</t>
+          <t>7082</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
@@ -14993,7 +14993,7 @@
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>4,71%</t>
+          <t>5,16%</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr">
@@ -15048,7 +15048,7 @@
       </c>
       <c r="T35" s="2" t="inlineStr">
         <is>
-          <t>5882</t>
+          <t>6535</t>
         </is>
       </c>
       <c r="U35" s="2" t="inlineStr">
@@ -15063,7 +15063,7 @@
       </c>
       <c r="W35" s="2" t="inlineStr">
         <is>
-          <t>2,09%</t>
+          <t>2,33%</t>
         </is>
       </c>
     </row>
@@ -15086,12 +15086,12 @@
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>27521</t>
+          <t>26790</t>
         </is>
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>44481</t>
+          <t>43599</t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr">
@@ -15101,12 +15101,12 @@
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t>20,03%</t>
+          <t>19,5%</t>
         </is>
       </c>
       <c r="I36" s="2" t="inlineStr">
         <is>
-          <t>32,38%</t>
+          <t>31,74%</t>
         </is>
       </c>
       <c r="J36" s="2" t="inlineStr">
@@ -15121,12 +15121,12 @@
       </c>
       <c r="L36" s="2" t="inlineStr">
         <is>
-          <t>28287</t>
+          <t>27186</t>
         </is>
       </c>
       <c r="M36" s="2" t="inlineStr">
         <is>
-          <t>44698</t>
+          <t>44167</t>
         </is>
       </c>
       <c r="N36" s="2" t="inlineStr">
@@ -15136,12 +15136,12 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>19,73%</t>
+          <t>18,96%</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
         <is>
-          <t>31,17%</t>
+          <t>30,8%</t>
         </is>
       </c>
       <c r="Q36" s="2" t="inlineStr">
@@ -15156,12 +15156,12 @@
       </c>
       <c r="S36" s="2" t="inlineStr">
         <is>
-          <t>60180</t>
+          <t>59863</t>
         </is>
       </c>
       <c r="T36" s="2" t="inlineStr">
         <is>
-          <t>83130</t>
+          <t>83099</t>
         </is>
       </c>
       <c r="U36" s="2" t="inlineStr">
@@ -15171,12 +15171,12 @@
       </c>
       <c r="V36" s="2" t="inlineStr">
         <is>
-          <t>21,43%</t>
+          <t>21,32%</t>
         </is>
       </c>
       <c r="W36" s="2" t="inlineStr">
         <is>
-          <t>29,61%</t>
+          <t>29,6%</t>
         </is>
       </c>
     </row>
@@ -15199,12 +15199,12 @@
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>75731</t>
+          <t>77707</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>94893</t>
+          <t>95029</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
@@ -15214,12 +15214,12 @@
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>55,13%</t>
+          <t>56,57%</t>
         </is>
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>69,08%</t>
+          <t>69,18%</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr">
@@ -15234,12 +15234,12 @@
       </c>
       <c r="L37" s="2" t="inlineStr">
         <is>
-          <t>86908</t>
+          <t>86848</t>
         </is>
       </c>
       <c r="M37" s="2" t="inlineStr">
         <is>
-          <t>104684</t>
+          <t>104759</t>
         </is>
       </c>
       <c r="N37" s="2" t="inlineStr">
@@ -15249,12 +15249,12 @@
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>60,61%</t>
+          <t>60,57%</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
         <is>
-          <t>73,01%</t>
+          <t>73,06%</t>
         </is>
       </c>
       <c r="Q37" s="2" t="inlineStr">
@@ -15269,12 +15269,12 @@
       </c>
       <c r="S37" s="2" t="inlineStr">
         <is>
-          <t>169457</t>
+          <t>168979</t>
         </is>
       </c>
       <c r="T37" s="2" t="inlineStr">
         <is>
-          <t>194615</t>
+          <t>194322</t>
         </is>
       </c>
       <c r="U37" s="2" t="inlineStr">
@@ -15284,12 +15284,12 @@
       </c>
       <c r="V37" s="2" t="inlineStr">
         <is>
-          <t>60,36%</t>
+          <t>60,19%</t>
         </is>
       </c>
       <c r="W37" s="2" t="inlineStr">
         <is>
-          <t>69,32%</t>
+          <t>69,21%</t>
         </is>
       </c>
     </row>
@@ -15429,12 +15429,12 @@
       </c>
       <c r="E39" s="2" t="inlineStr">
         <is>
-          <t>4767</t>
+          <t>4661</t>
         </is>
       </c>
       <c r="F39" s="2" t="inlineStr">
         <is>
-          <t>14136</t>
+          <t>14187</t>
         </is>
       </c>
       <c r="G39" s="2" t="inlineStr">
@@ -15444,12 +15444,12 @@
       </c>
       <c r="H39" s="2" t="inlineStr">
         <is>
-          <t>2,92%</t>
+          <t>2,85%</t>
         </is>
       </c>
       <c r="I39" s="2" t="inlineStr">
         <is>
-          <t>8,65%</t>
+          <t>8,68%</t>
         </is>
       </c>
       <c r="J39" s="2" t="inlineStr">
@@ -15464,12 +15464,12 @@
       </c>
       <c r="L39" s="2" t="inlineStr">
         <is>
-          <t>1460</t>
+          <t>1349</t>
         </is>
       </c>
       <c r="M39" s="2" t="inlineStr">
         <is>
-          <t>8170</t>
+          <t>7965</t>
         </is>
       </c>
       <c r="N39" s="2" t="inlineStr">
@@ -15479,12 +15479,12 @@
       </c>
       <c r="O39" s="2" t="inlineStr">
         <is>
-          <t>0,85%</t>
+          <t>0,79%</t>
         </is>
       </c>
       <c r="P39" s="2" t="inlineStr">
         <is>
-          <t>4,78%</t>
+          <t>4,66%</t>
         </is>
       </c>
       <c r="Q39" s="2" t="inlineStr">
@@ -15499,12 +15499,12 @@
       </c>
       <c r="S39" s="2" t="inlineStr">
         <is>
-          <t>7975</t>
+          <t>8016</t>
         </is>
       </c>
       <c r="T39" s="2" t="inlineStr">
         <is>
-          <t>19543</t>
+          <t>19489</t>
         </is>
       </c>
       <c r="U39" s="2" t="inlineStr">
@@ -15514,12 +15514,12 @@
       </c>
       <c r="V39" s="2" t="inlineStr">
         <is>
-          <t>2,39%</t>
+          <t>2,4%</t>
         </is>
       </c>
       <c r="W39" s="2" t="inlineStr">
         <is>
-          <t>5,85%</t>
+          <t>5,83%</t>
         </is>
       </c>
     </row>
@@ -15547,7 +15547,7 @@
       </c>
       <c r="F40" s="2" t="inlineStr">
         <is>
-          <t>5422</t>
+          <t>5614</t>
         </is>
       </c>
       <c r="G40" s="2" t="inlineStr">
@@ -15562,7 +15562,7 @@
       </c>
       <c r="I40" s="2" t="inlineStr">
         <is>
-          <t>3,32%</t>
+          <t>3,43%</t>
         </is>
       </c>
       <c r="J40" s="2" t="inlineStr">
@@ -15577,12 +15577,12 @@
       </c>
       <c r="L40" s="2" t="inlineStr">
         <is>
-          <t>673</t>
+          <t>676</t>
         </is>
       </c>
       <c r="M40" s="2" t="inlineStr">
         <is>
-          <t>6144</t>
+          <t>6416</t>
         </is>
       </c>
       <c r="N40" s="2" t="inlineStr">
@@ -15592,12 +15592,12 @@
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>0,39%</t>
+          <t>0,4%</t>
         </is>
       </c>
       <c r="P40" s="2" t="inlineStr">
         <is>
-          <t>3,6%</t>
+          <t>3,76%</t>
         </is>
       </c>
       <c r="Q40" s="2" t="inlineStr">
@@ -15612,12 +15612,12 @@
       </c>
       <c r="S40" s="2" t="inlineStr">
         <is>
-          <t>1918</t>
+          <t>1923</t>
         </is>
       </c>
       <c r="T40" s="2" t="inlineStr">
         <is>
-          <t>8789</t>
+          <t>8918</t>
         </is>
       </c>
       <c r="U40" s="2" t="inlineStr">
@@ -15627,12 +15627,12 @@
       </c>
       <c r="V40" s="2" t="inlineStr">
         <is>
-          <t>0,57%</t>
+          <t>0,58%</t>
         </is>
       </c>
       <c r="W40" s="2" t="inlineStr">
         <is>
-          <t>2,63%</t>
+          <t>2,67%</t>
         </is>
       </c>
     </row>
@@ -15655,12 +15655,12 @@
       </c>
       <c r="E41" s="2" t="inlineStr">
         <is>
-          <t>28583</t>
+          <t>27810</t>
         </is>
       </c>
       <c r="F41" s="2" t="inlineStr">
         <is>
-          <t>45747</t>
+          <t>44220</t>
         </is>
       </c>
       <c r="G41" s="2" t="inlineStr">
@@ -15670,12 +15670,12 @@
       </c>
       <c r="H41" s="2" t="inlineStr">
         <is>
-          <t>17,49%</t>
+          <t>17,01%</t>
         </is>
       </c>
       <c r="I41" s="2" t="inlineStr">
         <is>
-          <t>27,99%</t>
+          <t>27,05%</t>
         </is>
       </c>
       <c r="J41" s="2" t="inlineStr">
@@ -15690,12 +15690,12 @@
       </c>
       <c r="L41" s="2" t="inlineStr">
         <is>
-          <t>28546</t>
+          <t>28484</t>
         </is>
       </c>
       <c r="M41" s="2" t="inlineStr">
         <is>
-          <t>45892</t>
+          <t>45611</t>
         </is>
       </c>
       <c r="N41" s="2" t="inlineStr">
@@ -15705,12 +15705,12 @@
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>16,71%</t>
+          <t>16,67%</t>
         </is>
       </c>
       <c r="P41" s="2" t="inlineStr">
         <is>
-          <t>26,86%</t>
+          <t>26,7%</t>
         </is>
       </c>
       <c r="Q41" s="2" t="inlineStr">
@@ -15725,12 +15725,12 @@
       </c>
       <c r="S41" s="2" t="inlineStr">
         <is>
-          <t>60552</t>
+          <t>61576</t>
         </is>
       </c>
       <c r="T41" s="2" t="inlineStr">
         <is>
-          <t>85367</t>
+          <t>85169</t>
         </is>
       </c>
       <c r="U41" s="2" t="inlineStr">
@@ -15740,12 +15740,12 @@
       </c>
       <c r="V41" s="2" t="inlineStr">
         <is>
-          <t>18,11%</t>
+          <t>18,42%</t>
         </is>
       </c>
       <c r="W41" s="2" t="inlineStr">
         <is>
-          <t>25,54%</t>
+          <t>25,48%</t>
         </is>
       </c>
     </row>
@@ -15768,12 +15768,12 @@
       </c>
       <c r="E42" s="2" t="inlineStr">
         <is>
-          <t>106811</t>
+          <t>107345</t>
         </is>
       </c>
       <c r="F42" s="2" t="inlineStr">
         <is>
-          <t>126014</t>
+          <t>126032</t>
         </is>
       </c>
       <c r="G42" s="2" t="inlineStr">
@@ -15783,12 +15783,12 @@
       </c>
       <c r="H42" s="2" t="inlineStr">
         <is>
-          <t>65,35%</t>
+          <t>65,67%</t>
         </is>
       </c>
       <c r="I42" s="2" t="inlineStr">
         <is>
-          <t>77,1%</t>
+          <t>77,11%</t>
         </is>
       </c>
       <c r="J42" s="2" t="inlineStr">
@@ -15803,12 +15803,12 @@
       </c>
       <c r="L42" s="2" t="inlineStr">
         <is>
-          <t>117978</t>
+          <t>118171</t>
         </is>
       </c>
       <c r="M42" s="2" t="inlineStr">
         <is>
-          <t>136126</t>
+          <t>135909</t>
         </is>
       </c>
       <c r="N42" s="2" t="inlineStr">
@@ -15818,12 +15818,12 @@
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>69,05%</t>
+          <t>69,17%</t>
         </is>
       </c>
       <c r="P42" s="2" t="inlineStr">
         <is>
-          <t>79,68%</t>
+          <t>79,55%</t>
         </is>
       </c>
       <c r="Q42" s="2" t="inlineStr">
@@ -15838,12 +15838,12 @@
       </c>
       <c r="S42" s="2" t="inlineStr">
         <is>
-          <t>230953</t>
+          <t>232281</t>
         </is>
       </c>
       <c r="T42" s="2" t="inlineStr">
         <is>
-          <t>257046</t>
+          <t>256751</t>
         </is>
       </c>
       <c r="U42" s="2" t="inlineStr">
@@ -15853,12 +15853,12 @@
       </c>
       <c r="V42" s="2" t="inlineStr">
         <is>
-          <t>69,09%</t>
+          <t>69,48%</t>
         </is>
       </c>
       <c r="W42" s="2" t="inlineStr">
         <is>
-          <t>76,89%</t>
+          <t>76,8%</t>
         </is>
       </c>
     </row>
@@ -15998,12 +15998,12 @@
       </c>
       <c r="E44" s="2" t="inlineStr">
         <is>
-          <t>44459</t>
+          <t>45443</t>
         </is>
       </c>
       <c r="F44" s="2" t="inlineStr">
         <is>
-          <t>67429</t>
+          <t>69407</t>
         </is>
       </c>
       <c r="G44" s="2" t="inlineStr">
@@ -16013,12 +16013,12 @@
       </c>
       <c r="H44" s="2" t="inlineStr">
         <is>
-          <t>6,35%</t>
+          <t>6,49%</t>
         </is>
       </c>
       <c r="I44" s="2" t="inlineStr">
         <is>
-          <t>9,63%</t>
+          <t>9,91%</t>
         </is>
       </c>
       <c r="J44" s="2" t="inlineStr">
@@ -16033,12 +16033,12 @@
       </c>
       <c r="L44" s="2" t="inlineStr">
         <is>
-          <t>49890</t>
+          <t>50467</t>
         </is>
       </c>
       <c r="M44" s="2" t="inlineStr">
         <is>
-          <t>75597</t>
+          <t>76897</t>
         </is>
       </c>
       <c r="N44" s="2" t="inlineStr">
@@ -16048,12 +16048,12 @@
       </c>
       <c r="O44" s="2" t="inlineStr">
         <is>
-          <t>6,7%</t>
+          <t>6,78%</t>
         </is>
       </c>
       <c r="P44" s="2" t="inlineStr">
         <is>
-          <t>10,16%</t>
+          <t>10,33%</t>
         </is>
       </c>
       <c r="Q44" s="2" t="inlineStr">
@@ -16068,12 +16068,12 @@
       </c>
       <c r="S44" s="2" t="inlineStr">
         <is>
-          <t>100410</t>
+          <t>102634</t>
         </is>
       </c>
       <c r="T44" s="2" t="inlineStr">
         <is>
-          <t>134263</t>
+          <t>135872</t>
         </is>
       </c>
       <c r="U44" s="2" t="inlineStr">
@@ -16083,12 +16083,12 @@
       </c>
       <c r="V44" s="2" t="inlineStr">
         <is>
-          <t>6,95%</t>
+          <t>7,1%</t>
         </is>
       </c>
       <c r="W44" s="2" t="inlineStr">
         <is>
-          <t>9,29%</t>
+          <t>9,41%</t>
         </is>
       </c>
     </row>
@@ -16111,12 +16111,12 @@
       </c>
       <c r="E45" s="2" t="inlineStr">
         <is>
-          <t>10124</t>
+          <t>10658</t>
         </is>
       </c>
       <c r="F45" s="2" t="inlineStr">
         <is>
-          <t>23984</t>
+          <t>24300</t>
         </is>
       </c>
       <c r="G45" s="2" t="inlineStr">
@@ -16126,12 +16126,12 @@
       </c>
       <c r="H45" s="2" t="inlineStr">
         <is>
-          <t>1,45%</t>
+          <t>1,52%</t>
         </is>
       </c>
       <c r="I45" s="2" t="inlineStr">
         <is>
-          <t>3,42%</t>
+          <t>3,47%</t>
         </is>
       </c>
       <c r="J45" s="2" t="inlineStr">
@@ -16146,12 +16146,12 @@
       </c>
       <c r="L45" s="2" t="inlineStr">
         <is>
-          <t>6197</t>
+          <t>6155</t>
         </is>
       </c>
       <c r="M45" s="2" t="inlineStr">
         <is>
-          <t>17222</t>
+          <t>17172</t>
         </is>
       </c>
       <c r="N45" s="2" t="inlineStr">
@@ -16181,12 +16181,12 @@
       </c>
       <c r="S45" s="2" t="inlineStr">
         <is>
-          <t>18565</t>
+          <t>18406</t>
         </is>
       </c>
       <c r="T45" s="2" t="inlineStr">
         <is>
-          <t>35622</t>
+          <t>36353</t>
         </is>
       </c>
       <c r="U45" s="2" t="inlineStr">
@@ -16196,12 +16196,12 @@
       </c>
       <c r="V45" s="2" t="inlineStr">
         <is>
-          <t>1,29%</t>
+          <t>1,27%</t>
         </is>
       </c>
       <c r="W45" s="2" t="inlineStr">
         <is>
-          <t>2,47%</t>
+          <t>2,52%</t>
         </is>
       </c>
     </row>
@@ -16224,12 +16224,12 @@
       </c>
       <c r="E46" s="2" t="inlineStr">
         <is>
-          <t>143340</t>
+          <t>145741</t>
         </is>
       </c>
       <c r="F46" s="2" t="inlineStr">
         <is>
-          <t>181036</t>
+          <t>181763</t>
         </is>
       </c>
       <c r="G46" s="2" t="inlineStr">
@@ -16239,12 +16239,12 @@
       </c>
       <c r="H46" s="2" t="inlineStr">
         <is>
-          <t>20,46%</t>
+          <t>20,81%</t>
         </is>
       </c>
       <c r="I46" s="2" t="inlineStr">
         <is>
-          <t>25,84%</t>
+          <t>25,95%</t>
         </is>
       </c>
       <c r="J46" s="2" t="inlineStr">
@@ -16259,12 +16259,12 @@
       </c>
       <c r="L46" s="2" t="inlineStr">
         <is>
-          <t>149857</t>
+          <t>149442</t>
         </is>
       </c>
       <c r="M46" s="2" t="inlineStr">
         <is>
-          <t>187645</t>
+          <t>185994</t>
         </is>
       </c>
       <c r="N46" s="2" t="inlineStr">
@@ -16274,12 +16274,12 @@
       </c>
       <c r="O46" s="2" t="inlineStr">
         <is>
-          <t>20,14%</t>
+          <t>20,08%</t>
         </is>
       </c>
       <c r="P46" s="2" t="inlineStr">
         <is>
-          <t>25,22%</t>
+          <t>24,99%</t>
         </is>
       </c>
       <c r="Q46" s="2" t="inlineStr">
@@ -16294,12 +16294,12 @@
       </c>
       <c r="S46" s="2" t="inlineStr">
         <is>
-          <t>304455</t>
+          <t>304775</t>
         </is>
       </c>
       <c r="T46" s="2" t="inlineStr">
         <is>
-          <t>357538</t>
+          <t>356708</t>
         </is>
       </c>
       <c r="U46" s="2" t="inlineStr">
@@ -16309,12 +16309,12 @@
       </c>
       <c r="V46" s="2" t="inlineStr">
         <is>
-          <t>21,07%</t>
+          <t>21,1%</t>
         </is>
       </c>
       <c r="W46" s="2" t="inlineStr">
         <is>
-          <t>24,75%</t>
+          <t>24,69%</t>
         </is>
       </c>
     </row>
@@ -16337,12 +16337,12 @@
       </c>
       <c r="E47" s="2" t="inlineStr">
         <is>
-          <t>447027</t>
+          <t>444353</t>
         </is>
       </c>
       <c r="F47" s="2" t="inlineStr">
         <is>
-          <t>487702</t>
+          <t>485727</t>
         </is>
       </c>
       <c r="G47" s="2" t="inlineStr">
@@ -16352,12 +16352,12 @@
       </c>
       <c r="H47" s="2" t="inlineStr">
         <is>
-          <t>63,82%</t>
+          <t>63,43%</t>
         </is>
       </c>
       <c r="I47" s="2" t="inlineStr">
         <is>
-          <t>69,62%</t>
+          <t>69,34%</t>
         </is>
       </c>
       <c r="J47" s="2" t="inlineStr">
@@ -16372,12 +16372,12 @@
       </c>
       <c r="L47" s="2" t="inlineStr">
         <is>
-          <t>479772</t>
+          <t>483533</t>
         </is>
       </c>
       <c r="M47" s="2" t="inlineStr">
         <is>
-          <t>524566</t>
+          <t>524644</t>
         </is>
       </c>
       <c r="N47" s="2" t="inlineStr">
@@ -16387,12 +16387,12 @@
       </c>
       <c r="O47" s="2" t="inlineStr">
         <is>
-          <t>64,47%</t>
+          <t>64,98%</t>
         </is>
       </c>
       <c r="P47" s="2" t="inlineStr">
         <is>
-          <t>70,49%</t>
+          <t>70,5%</t>
         </is>
       </c>
       <c r="Q47" s="2" t="inlineStr">
@@ -16407,12 +16407,12 @@
       </c>
       <c r="S47" s="2" t="inlineStr">
         <is>
-          <t>939566</t>
+          <t>940932</t>
         </is>
       </c>
       <c r="T47" s="2" t="inlineStr">
         <is>
-          <t>998594</t>
+          <t>999045</t>
         </is>
       </c>
       <c r="U47" s="2" t="inlineStr">
@@ -16422,12 +16422,12 @@
       </c>
       <c r="V47" s="2" t="inlineStr">
         <is>
-          <t>65,04%</t>
+          <t>65,13%</t>
         </is>
       </c>
       <c r="W47" s="2" t="inlineStr">
         <is>
-          <t>69,12%</t>
+          <t>69,15%</t>
         </is>
       </c>
     </row>
